--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-53.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>449.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.5%</t>
+          <t>-688.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-274.2%</t>
+          <t>-251.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-189.2%</t>
+          <t>-175.5%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242297</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205902</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264167</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742303</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705329</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190772</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.21303558880677</v>
+        <v>-5.441588442287331</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6310529423293847</v>
+        <v>0.5396318009371606</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.183333464830477</v>
+        <v>-5.411886318311037</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6436171836818154</v>
+        <v>0.5521960422895913</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.003958043591709</v>
+        <v>-5.232510897072269</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7091543274837369</v>
+        <v>0.6177331860915127</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.048972257112315</v>
+        <v>-5.277525110592876</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6719560974070844</v>
+        <v>0.5805349560148598</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.31597676738475</v>
+        <v>-5.544529620865311</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5708458556370561</v>
+        <v>0.4794247142448316</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.417174548821922</v>
+        <v>-5.645727402302484</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5295706649586882</v>
+        <v>0.4381495235664636</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.38469896265115</v>
+        <v>-5.613251816131712</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.540160860981314</v>
+        <v>0.4487397195890894</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.365660834943853</v>
+        <v>-5.594213688424414</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5443008312724777</v>
+        <v>0.4528796898802532</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.396787466094471</v>
+        <v>-5.625340319575033</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7094320477509108</v>
+        <v>0.6180109063586863</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.449107846695263</v>
+        <v>-5.677660700175824</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.689337224496728</v>
+        <v>0.5979160831045034</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.469365145224221</v>
+        <v>-5.697917998704782</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6872428354820705</v>
+        <v>0.595821694089846</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.321622174989218</v>
+        <v>-5.55017502846978</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8254926713680937</v>
+        <v>0.7340715299758691</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.42363685752044</v>
+        <v>-5.652189711001001</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7874804198870859</v>
+        <v>0.6960592784948614</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.287027513426347</v>
+        <v>-5.515580366906908</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8427865059163815</v>
+        <v>0.7513653645241569</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.429792846248997</v>
+        <v>-5.658345699729558</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7847608495274314</v>
+        <v>0.6933397081352068</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.367494847472875</v>
+        <v>-5.596047700953436</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8760156028347015</v>
+        <v>0.7845944614424769</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.165704649807717</v>
+        <v>-5.394257503288278</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6653125542901628</v>
+        <v>0.5738914128979382</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.105813968165124</v>
+        <v>-5.334366821645685</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7595590592693751</v>
+        <v>0.6681379178771505</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.203554512790098</v>
+        <v>-5.432107366270659</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7350905775354288</v>
+        <v>0.6436694361432043</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.379892272913027</v>
+        <v>-5.608445126393589</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.663091454310929</v>
+        <v>0.5716703129187044</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.379202900751804</v>
+        <v>-5.607755754232365</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6618588212153469</v>
+        <v>0.5704376798231223</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.385773865806397</v>
+        <v>-5.614326719286958</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6590933026289458</v>
+        <v>0.5676721612367213</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.377819895511625</v>
+        <v>-5.606372748992186</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.662274890746855</v>
+        <v>0.5708537493546304</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.367446519178538</v>
+        <v>-5.595999372659099</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.672805998307894</v>
+        <v>0.5813848569156694</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.239762209384241</v>
+        <v>-5.468315062864803</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7287720956003376</v>
+        <v>0.6373509542081131</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.30042879978663</v>
+        <v>-5.528981653267191</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6912601319152545</v>
+        <v>0.5998389905230299</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.235434939852984</v>
+        <v>-5.463987793333546</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7213553784993412</v>
+        <v>0.6299342371071166</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674314</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.336193575609983</v>
+        <v>-5.564746429090544</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.68521286382762</v>
+        <v>0.5937917224353955</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.291990738524082</v>
+        <v>-5.520543592004644</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7087736011898174</v>
+        <v>0.6173524597975928</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.328969766187525</v>
+        <v>-5.557522619668086</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6923919905936877</v>
+        <v>0.6009708492014632</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.349027845052365</v>
+        <v>-5.577580698532927</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.735616524230791</v>
+        <v>0.6441953828385665</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.309097171874475</v>
+        <v>-5.537650025355036</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7500294980962003</v>
+        <v>0.6586083567039758</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5416340156901341</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.764622183762308</v>
+        <v>3.471742803044505</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.269390410828753</v>
+        <v>-5.268072957781768</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7608604307527593</v>
+        <v>0.7613874119715534</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.501927254644412</v>
+        <v>-0.2720569481168653</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.567816666611361</v>
+        <v>2.705738850527889</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.8%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.4%</t>
+          <t>-684.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-300.1%</t>
+          <t>-298.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.2%</t>
+          <t>-265.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-175.5%</t>
+          <t>-183.8%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-5.974308483644571</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7273446431515054</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.8297343157080034</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.619583871498279</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.339435866283318</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.580548205101838</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.126045100007016</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.441051915924703</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.748024643463996</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.4158742382443261</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.194660193631055</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.024600743779828</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.3004292305894536</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.189845626102516</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.440992618066826</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1318665314835319</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.187839676711393</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.757604560607474</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>0.01548044513595181</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.198098367380072</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.103479382592283</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1267699185122768</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.194197932525768</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.267059260776668</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.1937969497310297</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.534633877187694</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.192602852580769</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.563720602586866</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.3086825105259008</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.603377012921573</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.155135947069649</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.768751783361182</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.3947212873700305</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.603377012921573</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.151109642535246</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.151753172103813</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.548023944188667</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.603377012921573</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.151007541213662</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.333622963088848</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.6182003446112505</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.785246803906608</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>2.044457182594071</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.693153285592849</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.7566621703148009</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.785246803906608</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>2.049807485892122</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.743502349047072</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.7688857757393124</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.83559586736083</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>2.027514067776766</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.841121626468468</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.8048917360861019</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-1.933215144782227</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.971984251945697</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-9.98864771447411</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.8610086149667868</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.08074123278787</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.886362155463883</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.19290588980397</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9371986879800902</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.208380177401859</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.815291985814132</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.33471566401076</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-0.989440043178369</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.379658975047434</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.717007261711223</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.26124583234331</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-0.9446804090179688</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.306189143379986</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.776460862205113</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.43637024972986</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-1.000174955225069</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.48131356076653</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.685941432520703</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.67082234374435</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.101174957732461</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.48131356076653</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.678722267619107</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-10.95862618828158</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.222968686321332</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.769117405303768</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.499367770122788</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-11.01141234388191</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.242967358722907</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.864792891886165</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.443078268011907</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.1374491372502</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.290688347441108</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.839541269076423</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.460922970326866</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.08543362328139</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.265891806167182</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.839541269076423</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.464913306013267</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.22710546500551</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.324035769755572</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.839541269076423</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.463438079114526</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.17751462058067</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.289146021820766</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.789950424651589</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.508245995934298</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.1647072275759</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.297074198265539</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.838806199660489</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.465881397282275</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-10.93886207485649</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.197157064141565</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.796879524073326</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.500616475670782</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.8142834185189</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.14618645705047</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.796879524073326</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.501755620226841</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-10.86717870656318</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.164710798106077</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.79192417798488</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.507362602042016</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.7950455312753</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.130123823752288</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.79192417798488</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.513096306280652</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75867548422403</v>
+        <v>-10.72367913866565</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.125313067325643</v>
+        <v>-1.111314529102295</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.720557785375231</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.546178879452576</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.45984227146158</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-1.015663263533574</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.720557785375231</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.536295398139669</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22759681615156</v>
+        <v>-10.19260047059319</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9245996419089377</v>
+        <v>-0.9106011036855883</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.720557785375231</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.534460837640295</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12968977747507</v>
+        <v>-10.0946934319167</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8857371414118025</v>
+        <v>-0.8717386031884531</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.652572035514675</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.574951972583168</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10573623649911</v>
+        <v>-10.07073989094074</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8754872188759255</v>
+        <v>-0.8614886806525761</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.628618494538717</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.589992603314236</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.841676298176314</v>
+        <v>-9.806679952617941</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7831235597085588</v>
+        <v>-0.7691250214852099</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.364558556215921</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.735168250146161</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.134596674671476</v>
+        <v>-9.099600329113104</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5030787439669249</v>
+        <v>-0.4890802057435755</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.364558556215921</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.732381216485861</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.094412376305286</v>
+        <v>-9.059416030746913</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4866614007326073</v>
+        <v>-0.4726628625092579</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.324374257849731</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.756835419393416</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.014342580767481</v>
+        <v>-8.979346235209109</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4552666612967284</v>
+        <v>-0.4412681230733795</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.244304462311927</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.804244117936856</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.780861358537884</v>
+        <v>-8.745865012979511</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3539497435670369</v>
+        <v>-0.3399512053436879</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.010823240082328</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.952257280112467</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.631194967530369</v>
+        <v>-8.596198621971997</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2969753974769906</v>
+        <v>-0.2829768592536412</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-1.917919748839792</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>2.00510716454503</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.498919493899482</v>
+        <v>-8.463923148341109</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2486977212776087</v>
+        <v>-0.2346991830542593</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.785644275208905</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.079839935470589</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.308319819226329</v>
+        <v>-8.273323473667956</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1696427907207103</v>
+        <v>-0.1556442524973614</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.595044600535753</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.197014800962117</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.059320020542748</v>
+        <v>-8.024323674984375</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05713653002361907</v>
+        <v>-0.04313799180027011</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.595044600535753</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.209921142185776</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.164910010315852</v>
+        <v>-8.129913664757479</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2273484555320797</v>
+        <v>-0.2133499173087308</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.700634590308857</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>2.018591218722695</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.183644912434449</v>
+        <v>-8.148648566876076</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1862980745024321</v>
+        <v>-0.1722995362790831</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.706230599968988</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.063777954803702</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.03570487102685</v>
+        <v>-8.000708525468477</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2470009806275599</v>
+        <v>-0.233002442404211</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.685909684060431</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.956091581660669</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.018546720895555</v>
+        <v>-7.983550375337183</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2488517068285203</v>
+        <v>-0.2348531686051714</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.668751533929136</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.957672485485968</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.974998314124865</v>
+        <v>-7.940001968566492</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2383929562153373</v>
+        <v>-0.2243944179919883</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.668751533929136</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.950711873390874</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.732849920671007</v>
+        <v>-7.697853575112634</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1270712444526509</v>
+        <v>-0.113072706229302</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.668751533929136</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.965174227772017</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.624590783548485</v>
+        <v>-7.589594437990113</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08923546914444724</v>
+        <v>-0.07523693092109829</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.668751533929136</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.959706348231212</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501299648731354</v>
+        <v>-7.466303303172982</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04242092120701813</v>
+        <v>-0.02842238298366917</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.545460399112006</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.031179123132067</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480150449827911</v>
+        <v>-7.445154104269538</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02626026340831578</v>
+        <v>-0.01226172518496682</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.524311200208563</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.051569620711459</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236385007844467</v>
+        <v>-7.201388662286094</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06702662173211271</v>
+        <v>0.08102515995546167</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.524311200208563</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.04735032905851</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.134622187567172</v>
+        <v>-7.099625842008799</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1098560637630466</v>
+        <v>0.1238546019863955</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.511092131816134</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.057406084013983</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.884771793618097</v>
+        <v>-6.849775448059725</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2025382963263787</v>
+        <v>0.2165368345497276</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.511092131816134</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.050148158997685</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.708879701150664</v>
+        <v>-6.673883355592292</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2764942568340008</v>
+        <v>0.2904927950573497</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.511092131816134</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.053747282518334</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.537433238128201</v>
+        <v>-6.502436892569828</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3584003480975397</v>
+        <v>0.3723988863208887</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.339645668793671</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.169942666386365</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.312400238459378</v>
+        <v>-6.277403892901005</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4474340255813658</v>
+        <v>0.4614325638047148</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.114612669124848</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.303982943803956</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248764496225443</v>
+        <v>-6.213768150667071</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4775831235292567</v>
+        <v>0.4915816617526061</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.050976926890913</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.346859190198634</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.205002314919602</v>
+        <v>-6.170005969361229</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4762822548353891</v>
+        <v>0.4902807930587381</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.050976926890913</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.32805344898243</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.964571818114742</v>
+        <v>-5.929575472556369</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5741975301822109</v>
+        <v>0.5881960684055598</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.810546430086053</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.474054823690223</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.892329249943547</v>
+        <v>-5.857332904385174</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6070238712855089</v>
+        <v>0.6210224095088579</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.810546430086053</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.477984137525043</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.839330927662159</v>
+        <v>-5.804334582103786</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6289017841154041</v>
+        <v>0.642900322338753</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7552101710841141</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.511864476843547</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.730526042182432</v>
+        <v>-5.695529696624059</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6694218095272881</v>
+        <v>0.6834203477506371</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7552101710841141</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.50886254806354</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.510505244145421</v>
+        <v>-5.475508898587049</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7590091657527065</v>
+        <v>0.7730077039760554</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6139903260161339</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.595173492114943</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.377637555082144</v>
+        <v>-5.342641209523771</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8280504241798408</v>
+        <v>0.8420489624031902</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6139903260161339</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.611067674916766</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.218122451562774</v>
+        <v>-5.183126106004401</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8930023100278905</v>
+        <v>0.9070008482512399</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.454475222496764</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.70792258146869</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.073450306463037</v>
+        <v>-5.038453960904664</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9609592706292256</v>
+        <v>0.9749578088525745</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.3098030773970266</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.804813971089972</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.133325133820729</v>
+        <v>-5.098328788262356</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9230468310875746</v>
+        <v>0.9370453693109235</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3696779047547187</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.754926566076783</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.04652563604172</v>
+        <v>-5.011529290483347</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9801671235217442</v>
+        <v>0.9941656617450931</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3696779047547187</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.777327059399349</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.048995342503526</v>
+        <v>-5.013998996945153</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9792516423104338</v>
+        <v>0.9932501805337832</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.3721476112165248</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.775917636895677</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.117365528827536</v>
+        <v>-5.082369183269163</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9629104902555321</v>
+        <v>0.9769090284788811</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3628719121803099</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.792489978792108</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.22590370974367</v>
+        <v>-5.190907364185297</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9099319265209695</v>
+        <v>0.9239304647443185</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3628719121803099</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.782926687423999</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.256896869072375</v>
+        <v>-5.221900523514003</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7222442278298744</v>
+        <v>0.7362427660532234</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3628719121803099</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.607636252464386</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205902</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.081422609279906</v>
+        <v>-5.046426263721534</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7970011637386496</v>
+        <v>0.8109997019619986</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3628719121803099</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.612203484456174</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.192358861921155</v>
+        <v>-5.157362516362783</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7283686914433569</v>
+        <v>0.7423672296667063</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3628719121803099</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.587945513217381</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.395385439464389</v>
+        <v>-5.360389093906016</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6502894456459694</v>
+        <v>0.6642879838693183</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5658984897235433</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.469260951911346</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264167</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.237459840529096</v>
+        <v>-5.202463494970723</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7236320716522191</v>
+        <v>0.7376306098755681</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5658984897235433</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.479433338343479</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742303</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.151216377502718</v>
+        <v>-5.116220031944345</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7530757274366304</v>
+        <v>0.7670742656599794</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5658984897235433</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.474379608917339</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.196523196901698</v>
+        <v>-5.161526851343325</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7267287751215639</v>
+        <v>0.7407273133449128</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6067086527327741</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.441669286556326</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.225556301603999</v>
+        <v>-5.190559956045626</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7156674062737451</v>
+        <v>0.7296659444970941</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6067086527327741</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.442221159589428</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.132745820153139</v>
+        <v>-5.097749474594766</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6820642907454544</v>
+        <v>0.6960628289688038</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.5138981712819147</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.427180140351309</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.177135289482567</v>
+        <v>-5.142138943924194</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6661819789382846</v>
+        <v>0.6801805171616335</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.5582876406113424</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.402419934678253</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.064464071246316</v>
+        <v>-5.029467725687944</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7063261747445075</v>
+        <v>0.7203247129678565</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4456164223750922</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.465098374131726</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.952087070063643</v>
+        <v>-4.917090724505271</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.756768271048244</v>
+        <v>0.7707668092715929</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4456164223750922</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.470589669962393</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.150321638950374</v>
+        <v>-5.115325293392002</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6889716452620904</v>
+        <v>0.7029701834854398</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.6438509912618228</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.363146130398894</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.233322919975653</v>
+        <v>-5.198326574417281</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4941268528526321</v>
+        <v>0.5081253910759815</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6624218757889966</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.190359319683243</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.341936998418984</v>
+        <v>-5.306940652860612</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5708308821945054</v>
+        <v>0.5848294204178544</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6624218757889966</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.310508980402449</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190772</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.428535581400087</v>
+        <v>-5.393539235841715</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5507044751043875</v>
+        <v>0.5647030133277364</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6624218757889966</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.325022006504772</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.390151918841936</v>
+        <v>-5.355155573283564</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5634773814700162</v>
+        <v>0.5774759196933656</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6240382132308454</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.345471645382031</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.441588442287331</v>
+        <v>-5.178039243248397</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5396318009371606</v>
+        <v>0.6450514805527336</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6240382132308454</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.342200674227333</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.411886318311037</v>
+        <v>-5.148337119272104</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5521960422895913</v>
+        <v>0.6576157219051644</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7182873419843501</v>
+        <v>-0.6285083384461587</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.286334588737144</v>
+        <v>2.340201990860058</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.232510897072269</v>
+        <v>-4.968961698033336</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6177331860915127</v>
+        <v>0.7231528657070858</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5615105838136314</v>
+        <v>-0.47173158027544</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.374187618945989</v>
+        <v>2.428055021068904</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.277525110592876</v>
+        <v>-5.013975911553942</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5805349560148598</v>
+        <v>0.6859546356304334</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.591859479128236</v>
+        <v>-0.5020804755900447</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336785737088816</v>
+        <v>2.390653139211731</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.544529620865311</v>
+        <v>-5.280980421826377</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4794247142448316</v>
+        <v>0.5848443938604051</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7862225171711845</v>
+        <v>-0.6964435136329932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225859476601993</v>
+        <v>2.279726878724907</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.645727402302484</v>
+        <v>-5.38217820326355</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4381495235664636</v>
+        <v>0.5435692031820372</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.7648523271783123</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.184018110371303</v>
+        <v>2.237885512494217</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815461</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.613251816131712</v>
+        <v>-5.349702617092778</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4487397195890894</v>
+        <v>0.554159399204663</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.7648523271783123</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.18161807192562</v>
+        <v>2.235485474048534</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.594213688424414</v>
+        <v>-5.33066448938548</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4528796898802532</v>
+        <v>0.5582993694958267</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.8230359385095068</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.143232624335147</v>
+        <v>2.197100026458062</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131256</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.625340319575033</v>
+        <v>-5.361791120536099</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6180109063586863</v>
+        <v>0.7234305859742598</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.8230359385095068</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320814493273828</v>
+        <v>2.374681895396743</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.677660700175824</v>
+        <v>-5.41411150113689</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.5979160831045034</v>
+        <v>0.7033357627200769</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.7880890785006347</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.342615938265285</v>
+        <v>2.3964833403882</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.697917998704782</v>
+        <v>-5.434368799665848</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.595821694089846</v>
+        <v>0.7012413737054195</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.7880890785006347</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.348624468662211</v>
+        <v>2.402491870785126</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.55017502846978</v>
+        <v>-5.286625829430846</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7340715299758691</v>
+        <v>0.8394912095914426</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.6202817212657515</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.528461530795163</v>
+        <v>2.582328932918077</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.652189711001001</v>
+        <v>-5.388640511962067</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6960592784948614</v>
+        <v>0.8014789581104349</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.6202817212657515</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.531255152326644</v>
+        <v>2.585122554449558</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.515580366906908</v>
+        <v>-5.252031167867974</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7513653645241569</v>
+        <v>0.8567850441397304</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5734513807098505</v>
+        <v>-0.4836723771716591</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613883107174757</v>
+        <v>2.667750509297672</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.658345699729558</v>
+        <v>-5.394796500690624</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6933397081352068</v>
+        <v>0.7987593877507808</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.6264377099943095</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.527304384221277</v>
+        <v>2.581171786344192</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.596047700953436</v>
+        <v>-5.332498501914502</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7845944614424769</v>
+        <v>0.8900141410580504</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.6264377099943095</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.593639938018098</v>
+        <v>2.647507340141013</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.394257503288278</v>
+        <v>-5.130708304249344</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5738914128979382</v>
+        <v>0.6793110925135117</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5181985213633464</v>
+        <v>-0.4284195178251551</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.474899127831904</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.334366821645685</v>
+        <v>-5.070817622606751</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6681379178771505</v>
+        <v>0.773557597492724</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.458307839720753</v>
+        <v>-0.3685288361825616</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.581123769139635</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.432107366270659</v>
+        <v>-5.168558167231725</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6436694361432043</v>
+        <v>0.7490891157587782</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4741971178537331</v>
+        <v>-0.3844181143155418</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.586217938375891</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.608445126393589</v>
+        <v>-5.344895927354655</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5716703129187044</v>
+        <v>0.6770899925342779</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.5607558744384712</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.478951263126805</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.607755754232365</v>
+        <v>-5.344206555193431</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5704376798231223</v>
+        <v>0.6758573594386958</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.5607558744384712</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.477442881166733</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.614326719286958</v>
+        <v>-5.350777520248024</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5676721612367213</v>
+        <v>0.6730918408522948</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.5673268394930642</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.473363169569414</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.606372748992186</v>
+        <v>-5.342823549953252</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5708537493546304</v>
+        <v>0.6762734289702039</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.5673268394930642</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.473363169569414</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.595999372659099</v>
+        <v>-5.332450173620165</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5813848569156694</v>
+        <v>0.6868045365312434</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6467324666981682</v>
+        <v>-0.5569534631599768</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.485968952397071</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.468315062864803</v>
+        <v>-5.204765863825869</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6373509542081131</v>
+        <v>0.7427706338236866</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5190481569038717</v>
+        <v>-0.4292691533656804</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.567471911648374</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.528981653267191</v>
+        <v>-5.265432454228257</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.5998389905230299</v>
+        <v>0.7052586701386034</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6007464736224054</v>
+        <v>-0.5109674700842141</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.505207594093125</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690031</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.463987793333546</v>
+        <v>-5.200438594294612</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6299342371071166</v>
+        <v>0.7353539167226901</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.57391585901825</v>
+        <v>-0.4841368554800587</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.525403665466247</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674314</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.564746429090544</v>
+        <v>-5.30119723005161</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5937917224353955</v>
+        <v>0.699211402050969</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6627414277452555</v>
+        <v>-0.5729624242070641</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.476269263861122</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163224</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.520543592004644</v>
+        <v>-5.256994392965709</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6173524597975928</v>
+        <v>0.7227721394131663</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.618538590659355</v>
+        <v>-0.5287595871211637</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.5086705686405</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022909</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.557522619668086</v>
+        <v>-5.293973420629152</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6009708492014632</v>
+        <v>0.7063905288170367</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.4917856853298331</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.475397508061631</v>
+        <v>2.529264910184545</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042143</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.577580698532927</v>
+        <v>-5.314031499493993</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6441953828385665</v>
+        <v>0.74961506245414</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.4917856853298331</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.52664527324467</v>
+        <v>2.580512675367585</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.537650025355036</v>
+        <v>-5.274100826316102</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6586083567039758</v>
+        <v>0.7640280363195493</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5416340156901341</v>
+        <v>-0.4518550121519428</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.549044381745658</v>
+        <v>2.602911783868572</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.471742803044505</v>
+        <v>3.795333091573709</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.268072957781768</v>
+        <v>-5.233630478753398</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7613874119715534</v>
+        <v>0.7751644035829015</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2720569481168653</v>
+        <v>-0.4113846645892378</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.705738850527889</v>
+        <v>2.622142220644465</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-52.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.9%</t>
+          <t>-684.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.1%</t>
+          <t>-242.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.8%</t>
+          <t>-150.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1987"/>
+  <dimension ref="A1:G1988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.974308483644571</v>
+        <v>-5.975575025276293</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7273446431515054</v>
+        <v>0.7268380264988168</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8297343157080034</v>
+        <v>-0.8305261922551981</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.619583871498279</v>
+        <v>2.619108745569963</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.339435866283318</v>
+        <v>-6.34070240791504</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.580548205101838</v>
+        <v>0.5800415884491494</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.126045100007016</v>
+        <v>-1.126836976554211</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.441051915924703</v>
+        <v>2.440576789996387</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.748024643463996</v>
+        <v>-6.749291185095718</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4158742382443261</v>
+        <v>0.4153676215916371</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.194660193631055</v>
+        <v>2.194185067702739</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.024600743779828</v>
+        <v>-7.02586728541155</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3004292305894536</v>
+        <v>0.299922613936765</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.189845626102516</v>
+        <v>2.189370500174199</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.440992618066826</v>
+        <v>-7.442259159698548</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1318665314835319</v>
+        <v>0.1313599148308433</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.187839676711393</v>
+        <v>2.187364550783077</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.757604560607474</v>
+        <v>-7.758871102239196</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01548044513595181</v>
+        <v>0.01497382848326279</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.198098367380072</v>
+        <v>2.197623241451756</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.103479382592283</v>
+        <v>-8.104745924224005</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1267699185122768</v>
+        <v>-0.1272765351649654</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.194197932525768</v>
+        <v>2.193722806597451</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.267059260776668</v>
+        <v>-8.268325802408389</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1937969497310297</v>
+        <v>-0.1943035663837183</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.534633877187694</v>
+        <v>-1.535425753734889</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.192602852580769</v>
+        <v>2.192127726652452</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.563720602586866</v>
+        <v>-8.564987144218588</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3086825105259008</v>
+        <v>-0.3091891271785894</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.603377012921573</v>
+        <v>-1.604168889468768</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.155135947069649</v>
+        <v>2.154660821141333</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.768751783361182</v>
+        <v>-8.770018324992904</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3947212873700305</v>
+        <v>-0.3952279040227191</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.603377012921573</v>
+        <v>-1.604168889468768</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.151109642535246</v>
+        <v>2.15063451660693</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.151753172103813</v>
+        <v>-9.153019713735535</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.548023944188667</v>
+        <v>-0.5485305608413555</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.603377012921573</v>
+        <v>-1.604168889468768</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.151007541213662</v>
+        <v>2.150532415285346</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.333622963088848</v>
+        <v>-9.33488950472057</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6182003446112505</v>
+        <v>-0.6187069612639395</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.785246803906608</v>
+        <v>-1.786038680453803</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.044457182594071</v>
+        <v>2.043982056665754</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.693153285592849</v>
+        <v>-9.694419827224571</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7566621703148009</v>
+        <v>-0.7571687869674899</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.785246803906608</v>
+        <v>-1.786038680453803</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.049807485892122</v>
+        <v>2.049332359963805</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.743502349047072</v>
+        <v>-9.744768890678793</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7688857757393124</v>
+        <v>-0.769392392392001</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.83559586736083</v>
+        <v>-1.836387743908025</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.027514067776766</v>
+        <v>2.027038941848449</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.841121626468468</v>
+        <v>-9.842388168100189</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8048917360861019</v>
+        <v>-0.8053983527387909</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.933215144782227</v>
+        <v>-1.934007021329421</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.971984251945697</v>
+        <v>1.97150912601738</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.98864771447411</v>
+        <v>-9.989914256105832</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8610086149667868</v>
+        <v>-0.8615152316194759</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.08074123278787</v>
+        <v>-2.081533109335065</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.886362155463883</v>
+        <v>1.885887029535566</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.19290588980397</v>
+        <v>-10.1941724314357</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9371986879800902</v>
+        <v>-0.9377053046327788</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.208380177401859</v>
+        <v>-2.209172053949054</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.815291985814132</v>
+        <v>1.814816859885815</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.33471566401076</v>
+        <v>-10.33598220564248</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.989440043178369</v>
+        <v>-0.9899466598310576</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.379658975047434</v>
+        <v>-2.380450851594629</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.717007261711223</v>
+        <v>1.716532135782906</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26124583234331</v>
+        <v>-10.26251237397504</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9446804090179688</v>
+        <v>-0.9451870256706574</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.306189143379986</v>
+        <v>-2.306981019927181</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.776460862205113</v>
+        <v>1.775985736276796</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.43637024972986</v>
+        <v>-10.43763679136158</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.000174955225069</v>
+        <v>-1.000681571877758</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.48131356076653</v>
+        <v>-2.482105437313725</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.685941432520703</v>
+        <v>1.685466306592386</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67082234374435</v>
+        <v>-10.67208888537607</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.101174957732461</v>
+        <v>-1.10168157438515</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.48131356076653</v>
+        <v>-2.482105437313725</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.678722267619107</v>
+        <v>1.67824714169079</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.95862618828158</v>
+        <v>-10.95989272991331</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.222968686321332</v>
+        <v>-1.223475302974021</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.769117405303768</v>
+        <v>-2.769909281850963</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.499367770122788</v>
+        <v>1.498892644194471</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.01141234388191</v>
+        <v>-11.01267888551363</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.242967358722907</v>
+        <v>-1.243473975375595</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.864792891886165</v>
+        <v>-2.86558476843336</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.443078268011907</v>
+        <v>1.44260314208359</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.1374491372502</v>
+        <v>-11.13871567888192</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.290688347441108</v>
+        <v>-1.291194964093796</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.839541269076423</v>
+        <v>-2.840333145623617</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.460922970326866</v>
+        <v>1.46044784439855</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.08543362328139</v>
+        <v>-11.08670016491311</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.265891806167182</v>
+        <v>-1.26639842281987</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.839541269076423</v>
+        <v>-2.840333145623617</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.464913306013267</v>
+        <v>1.46443818008495</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.22710546500551</v>
+        <v>-11.22837200663723</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.324035769755572</v>
+        <v>-1.32454238640826</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.839541269076423</v>
+        <v>-2.840333145623617</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.463438079114526</v>
+        <v>1.462962953186209</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.17751462058067</v>
+        <v>-11.1787811622124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.289146021820766</v>
+        <v>-1.289652638473454</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.789950424651589</v>
+        <v>-2.790742301198784</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508245995934298</v>
+        <v>1.507770870005981</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.1647072275759</v>
+        <v>-11.16597376920762</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.297074198265539</v>
+        <v>-1.297580814918228</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.838806199660489</v>
+        <v>-2.839598076207685</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.465881397282275</v>
+        <v>1.465406271353958</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.93886207485649</v>
+        <v>-10.94012861648821</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.197157064141565</v>
+        <v>-1.197663680794255</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.796879524073326</v>
+        <v>-2.797671400620521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.500616475670782</v>
+        <v>1.500141349742464</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.8142834185189</v>
+        <v>-10.81554996015062</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.14618645705047</v>
+        <v>-1.146693073703159</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.796879524073326</v>
+        <v>-2.797671400620521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.501755620226841</v>
+        <v>1.501280494298523</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.86717870656318</v>
+        <v>-10.8684452481949</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.164710798106077</v>
+        <v>-1.165217414758765</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.79192417798488</v>
+        <v>-2.792716054532075</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.507362602042016</v>
+        <v>1.506887476113699</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.7950455312753</v>
+        <v>-10.79631207290702</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.130123823752288</v>
+        <v>-1.130630440404977</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.79192417798488</v>
+        <v>-2.792716054532075</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.513096306280652</v>
+        <v>1.512621180352335</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.72367913866565</v>
+        <v>-10.72494568029738</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.111314529102295</v>
+        <v>-1.111821145754983</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.720557785375231</v>
+        <v>-2.721349661922427</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.546178879452576</v>
+        <v>1.545703753524259</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.45984227146158</v>
+        <v>-10.46110881309331</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.015663263533574</v>
+        <v>-1.016169880186263</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.720557785375231</v>
+        <v>-2.721349661922427</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.536295398139669</v>
+        <v>1.535820272211351</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.19260047059319</v>
+        <v>-10.19386701222491</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9106011036855883</v>
+        <v>-0.9111077203382769</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.720557785375231</v>
+        <v>-2.721349661922427</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.534460837640295</v>
+        <v>1.533985711711978</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.0946934319167</v>
+        <v>-10.09595997354842</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8717386031884531</v>
+        <v>-0.8722452198411417</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.652572035514675</v>
+        <v>-2.65336391206187</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.574951972583168</v>
+        <v>1.574476846654851</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07073989094074</v>
+        <v>-10.07200643257246</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8614886806525761</v>
+        <v>-0.8619952973052647</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.628618494538717</v>
+        <v>-2.629410371085913</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.589992603314236</v>
+        <v>1.589517477385919</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.806679952617941</v>
+        <v>-9.807946494249663</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7691250214852099</v>
+        <v>-0.7696316381378985</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.364558556215921</v>
+        <v>-2.365350432763117</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.735168250146161</v>
+        <v>1.734693124217844</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.099600329113104</v>
+        <v>-9.100866870744825</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4890802057435755</v>
+        <v>-0.4895868223962645</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.364558556215921</v>
+        <v>-2.365350432763117</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.732381216485861</v>
+        <v>1.731906090557543</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.059416030746913</v>
+        <v>-9.060682572378635</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4726628625092579</v>
+        <v>-0.473169479161947</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.324374257849731</v>
+        <v>-2.325166134396926</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.756835419393416</v>
+        <v>1.756360293465099</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.979346235209109</v>
+        <v>-8.980612776840831</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4412681230733795</v>
+        <v>-0.4417747397260681</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.244304462311927</v>
+        <v>-2.245096338859122</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.804244117936856</v>
+        <v>1.803768992008539</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.745865012979511</v>
+        <v>-8.747131554611233</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3399512053436879</v>
+        <v>-0.3404578219963765</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.010823240082328</v>
+        <v>-2.011615116629523</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.952257280112467</v>
+        <v>1.95178215418415</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.596198621971997</v>
+        <v>-8.597465163603719</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2829768592536412</v>
+        <v>-0.2834834759063303</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.917919748839792</v>
+        <v>-1.918711625386987</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.00510716454503</v>
+        <v>2.004632038616712</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.463923148341109</v>
+        <v>-8.465189689972831</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2346991830542593</v>
+        <v>-0.2352057997069483</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.785644275208905</v>
+        <v>-1.786436151756101</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.079839935470589</v>
+        <v>2.079364809542271</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.273323473667956</v>
+        <v>-8.274590015299678</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1556442524973614</v>
+        <v>-0.1561508691500499</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.595044600535753</v>
+        <v>-1.595836477082948</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.197014800962117</v>
+        <v>2.1965396750338</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.024323674984375</v>
+        <v>-8.025590216616097</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.04313799180027011</v>
+        <v>-0.04364460845295914</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.595044600535753</v>
+        <v>-1.595836477082948</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.209921142185776</v>
+        <v>2.209446016257459</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.129913664757479</v>
+        <v>-8.131180206389201</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2133499173087308</v>
+        <v>-0.2138565339614193</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.700634590308857</v>
+        <v>-1.701426466856052</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.018591218722695</v>
+        <v>2.018116092794378</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.148648566876076</v>
+        <v>-8.149915108507798</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1722995362790831</v>
+        <v>-0.1728061529317717</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.706230599968988</v>
+        <v>-1.707022476516183</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.063777954803702</v>
+        <v>2.063302828875385</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.000708525468477</v>
+        <v>-8.001975067100199</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.233002442404211</v>
+        <v>-0.2335090590568996</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.685909684060431</v>
+        <v>-1.686701560607626</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.956091581660669</v>
+        <v>1.955616455732352</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.983550375337183</v>
+        <v>-7.984816916968905</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2348531686051714</v>
+        <v>-0.2353597852578604</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.668751533929136</v>
+        <v>-1.669543410476332</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.957672485485968</v>
+        <v>1.95719735955765</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.940001968566492</v>
+        <v>-7.941268510198214</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2243944179919883</v>
+        <v>-0.2249010346446774</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.668751533929136</v>
+        <v>-1.669543410476332</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.950711873390874</v>
+        <v>1.950236747462557</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.697853575112634</v>
+        <v>-7.699120116744356</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.113072706229302</v>
+        <v>-0.113579322881991</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.668751533929136</v>
+        <v>-1.669543410476332</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.965174227772017</v>
+        <v>1.9646991018437</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.589594437990113</v>
+        <v>-7.590860979621834</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.07523693092109829</v>
+        <v>-0.07574354757378732</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.668751533929136</v>
+        <v>-1.669543410476332</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.959706348231212</v>
+        <v>1.959231222302895</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.466303303172982</v>
+        <v>-7.467569844804704</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02842238298366917</v>
+        <v>-0.02892899963635776</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.545460399112006</v>
+        <v>-1.546252275659201</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.031179123132067</v>
+        <v>2.030703997203751</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.445154104269538</v>
+        <v>-7.44642064590126</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.01226172518496682</v>
+        <v>-0.01276834183765541</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.524311200208563</v>
+        <v>-1.525103076755758</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.051569620711459</v>
+        <v>2.051094494783142</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.201388662286094</v>
+        <v>-7.202655203917816</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08102515995546167</v>
+        <v>0.08051854330277308</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.524311200208563</v>
+        <v>-1.525103076755758</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.04735032905851</v>
+        <v>2.046875203130192</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.099625842008799</v>
+        <v>-7.100892383640521</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1238546019863955</v>
+        <v>0.1233479853337069</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.511092131816134</v>
+        <v>-1.511884008363329</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.057406084013983</v>
+        <v>2.056930958085665</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.849775448059725</v>
+        <v>-6.851041989691447</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2165368345497276</v>
+        <v>0.216030217897039</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.511092131816134</v>
+        <v>-1.511884008363329</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.050148158997685</v>
+        <v>2.049673033069368</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.673883355592292</v>
+        <v>-6.675149897224014</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2904927950573497</v>
+        <v>0.2899861784046607</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.511092131816134</v>
+        <v>-1.511884008363329</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.053747282518334</v>
+        <v>2.053272156590016</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.502436892569828</v>
+        <v>-6.50370343420155</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3723988863208887</v>
+        <v>0.3718922696682001</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.339645668793671</v>
+        <v>-1.340437545340866</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.169942666386365</v>
+        <v>2.169467540458048</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.277403892901005</v>
+        <v>-6.278670434532727</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4614325638047148</v>
+        <v>0.4609259471520262</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.114612669124848</v>
+        <v>-1.115404545672043</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.303982943803956</v>
+        <v>2.303507817875639</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.213768150667071</v>
+        <v>-6.215034692298793</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4915816617526061</v>
+        <v>0.4910750450999171</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.050976926890913</v>
+        <v>-1.051768803438109</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.346859190198634</v>
+        <v>2.346384064270317</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.170005969361229</v>
+        <v>-6.171272510992951</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4902807930587381</v>
+        <v>0.4897741764060495</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.050976926890913</v>
+        <v>-1.051768803438109</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.32805344898243</v>
+        <v>2.327578323054112</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.929575472556369</v>
+        <v>-5.930842014188091</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5881960684055598</v>
+        <v>0.5876894517528708</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.810546430086053</v>
+        <v>-0.8113383066332482</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.474054823690223</v>
+        <v>2.473579697761906</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.857332904385174</v>
+        <v>-5.858599446016896</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6210224095088579</v>
+        <v>0.6205157928561689</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.810546430086053</v>
+        <v>-0.8113383066332482</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.477984137525043</v>
+        <v>2.477509011596726</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.804334582103786</v>
+        <v>-5.805601123735508</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.642900322338753</v>
+        <v>0.642393705686064</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7552101710841141</v>
+        <v>-0.7560020476313094</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.511864476843547</v>
+        <v>2.51138935091523</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.695529696624059</v>
+        <v>-5.696796238255781</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6834203477506371</v>
+        <v>0.6829137310979485</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7552101710841141</v>
+        <v>-0.7560020476313094</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.50886254806354</v>
+        <v>2.508387422135223</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.475508898587049</v>
+        <v>-5.476775440218771</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7730077039760554</v>
+        <v>0.7725010873233669</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6139903260161339</v>
+        <v>-0.6147822025633292</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.595173492114943</v>
+        <v>2.594698366186625</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.342641209523771</v>
+        <v>-5.343907751155493</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8420489624031902</v>
+        <v>0.8415423457505011</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6139903260161339</v>
+        <v>-0.6147822025633292</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.611067674916766</v>
+        <v>2.610592548988449</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.183126106004401</v>
+        <v>-5.184392647636123</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9070008482512399</v>
+        <v>0.9064942315985509</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.454475222496764</v>
+        <v>-0.4552670990439592</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.70792258146869</v>
+        <v>2.707447455540372</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.038453960904664</v>
+        <v>-5.039720502536386</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9749578088525745</v>
+        <v>0.974451192199886</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3098030773970266</v>
+        <v>-0.3105949539442218</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.804813971089972</v>
+        <v>2.804338845161655</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.098328788262356</v>
+        <v>-5.099595329894078</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9370453693109235</v>
+        <v>0.9365387526582349</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3696779047547187</v>
+        <v>-0.3704697813019139</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.754926566076783</v>
+        <v>2.754451440148465</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.011529290483347</v>
+        <v>-5.012795832115069</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9941656617450931</v>
+        <v>0.9936590450924045</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3696779047547187</v>
+        <v>-0.3704697813019139</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.777327059399349</v>
+        <v>2.776851933471031</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.013998996945153</v>
+        <v>-5.015265538576875</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9932501805337832</v>
+        <v>0.9927435638810942</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3721476112165248</v>
+        <v>-0.3729394877637201</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.775917636895677</v>
+        <v>2.77544251096736</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.082369183269163</v>
+        <v>-5.083635724900885</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9769090284788811</v>
+        <v>0.976402411826192</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3628719121803099</v>
+        <v>-0.3636637887275052</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.792489978792108</v>
+        <v>2.792014852863791</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.190907364185297</v>
+        <v>-5.192173905817019</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9239304647443185</v>
+        <v>0.9234238480916299</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3628719121803099</v>
+        <v>-0.3636637887275052</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.782926687423999</v>
+        <v>2.782451561495682</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.221900523514003</v>
+        <v>-5.223167065145724</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7362427660532234</v>
+        <v>0.7357361494005348</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3628719121803099</v>
+        <v>-0.3636637887275052</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.607636252464386</v>
+        <v>2.607161126536069</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.046426263721534</v>
+        <v>-5.047692805353256</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8109997019619986</v>
+        <v>0.81049308530931</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3628719121803099</v>
+        <v>-0.3636637887275052</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.612203484456174</v>
+        <v>2.611728358527857</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.157362516362783</v>
+        <v>-5.158629057994505</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7423672296667063</v>
+        <v>0.7418606130140173</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3628719121803099</v>
+        <v>-0.3636637887275052</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.587945513217381</v>
+        <v>2.587470387289064</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.360389093906016</v>
+        <v>-5.361655635537738</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6642879838693183</v>
+        <v>0.6637813672166297</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5658984897235433</v>
+        <v>-0.5666903662707385</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.469260951911346</v>
+        <v>2.468785825983029</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.202463494970723</v>
+        <v>-5.203730036602445</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7376306098755681</v>
+        <v>0.737123993222879</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5658984897235433</v>
+        <v>-0.5666903662707385</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.479433338343479</v>
+        <v>2.478958212415161</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.116220031944345</v>
+        <v>-5.117486573576067</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7670742656599794</v>
+        <v>0.7665676490072908</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5658984897235433</v>
+        <v>-0.5666903662707385</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.474379608917339</v>
+        <v>2.473904482989022</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.161526851343325</v>
+        <v>-5.162793392975047</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7407273133449128</v>
+        <v>0.7402206966922242</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6067086527327741</v>
+        <v>-0.6075005292799693</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.441669286556326</v>
+        <v>2.441194160628009</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.190559956045626</v>
+        <v>-5.191826497677348</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7296659444970941</v>
+        <v>0.7291593278444055</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6067086527327741</v>
+        <v>-0.6075005292799693</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.442221159589428</v>
+        <v>2.441746033661111</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.097749474594766</v>
+        <v>-5.099016016226488</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6960628289688038</v>
+        <v>0.6955562123161148</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5138981712819147</v>
+        <v>-0.51469004782911</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.427180140351309</v>
+        <v>2.426705014422992</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.142138943924194</v>
+        <v>-5.143405485555916</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6801805171616335</v>
+        <v>0.6796739005089445</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5582876406113424</v>
+        <v>-0.5590795171585377</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.402419934678253</v>
+        <v>2.401944808749936</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.029467725687944</v>
+        <v>-5.030734267319666</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7203247129678565</v>
+        <v>0.7198180963151679</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4456164223750922</v>
+        <v>-0.4464082989222874</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.465098374131726</v>
+        <v>2.464623248203409</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.917090724505271</v>
+        <v>-4.918357266136993</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7707668092715929</v>
+        <v>0.7702601926189041</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4456164223750922</v>
+        <v>-0.4464082989222874</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.470589669962393</v>
+        <v>2.470114544034076</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.115325293392002</v>
+        <v>-5.116591835023724</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7029701834854398</v>
+        <v>0.7024635668327508</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6438509912618228</v>
+        <v>-0.644642867809018</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.363146130398894</v>
+        <v>2.362671004470577</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.198326574417281</v>
+        <v>-5.199593116049003</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5081253910759815</v>
+        <v>0.5076187744232925</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6624218757889966</v>
+        <v>-0.6632137523361918</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.190359319683243</v>
+        <v>2.189884193754926</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.306940652860612</v>
+        <v>-5.308207194492334</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5848294204178544</v>
+        <v>0.5843228037651658</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6624218757889966</v>
+        <v>-0.6632137523361918</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.310508980402449</v>
+        <v>2.310033854474132</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.393539235841715</v>
+        <v>-5.394805777473437</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5647030133277364</v>
+        <v>0.5641963966750474</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6624218757889966</v>
+        <v>-0.6632137523361918</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.325022006504772</v>
+        <v>2.324546880576455</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.355155573283564</v>
+        <v>-5.356422114915286</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5774759196933656</v>
+        <v>0.5769693030406766</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6240382132308454</v>
+        <v>-0.6248300897780407</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.345471645382031</v>
+        <v>2.344996519453714</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.178039243248397</v>
+        <v>-5.40785863836068</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6450514805527336</v>
+        <v>0.5531237225078209</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6240382132308454</v>
+        <v>-0.6248300897780407</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.342200674227333</v>
+        <v>2.341725548299016</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.148337119272104</v>
+        <v>-5.378156514384386</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6576157219051644</v>
+        <v>0.5656879638602512</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6285083384461587</v>
+        <v>-0.629300214993354</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.340201990860058</v>
+        <v>2.339726864931741</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.968961698033336</v>
+        <v>-5.198781093145619</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7231528657070858</v>
+        <v>0.6312251076621727</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.47173158027544</v>
+        <v>-0.4725234568226353</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.428055021068904</v>
+        <v>2.427579895140587</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.013975911553942</v>
+        <v>-5.243795306666225</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6859546356304334</v>
+        <v>0.5940268775855198</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5020804755900447</v>
+        <v>-0.5028723521372399</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.390653139211731</v>
+        <v>2.390178013283414</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.280980421826377</v>
+        <v>-5.51079981693866</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5848443938604051</v>
+        <v>0.4929166358154915</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6964435136329932</v>
+        <v>-0.6972353901801884</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.279726878724907</v>
+        <v>2.27925175279659</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.38217820326355</v>
+        <v>-5.611997598375833</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5435692031820372</v>
+        <v>0.451641445137124</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7648523271783123</v>
+        <v>-0.7656442037255076</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.237885512494217</v>
+        <v>2.2374103865659</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.349702617092778</v>
+        <v>-5.579522012205061</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.554159399204663</v>
+        <v>0.4622316411597498</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7648523271783123</v>
+        <v>-0.7656442037255076</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.235485474048534</v>
+        <v>2.235010348120217</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.33066448938548</v>
+        <v>-5.560483884497764</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5582993694958267</v>
+        <v>0.4663716114509135</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8230359385095068</v>
+        <v>-0.8238278150567021</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.197100026458062</v>
+        <v>2.196624900529745</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.361791120536099</v>
+        <v>-5.591610515648382</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7234305859742598</v>
+        <v>0.6315028279293466</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8230359385095068</v>
+        <v>-0.8238278150567021</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.374681895396743</v>
+        <v>2.374206769468426</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.41411150113689</v>
+        <v>-5.643930896249174</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7033357627200769</v>
+        <v>0.6114080046751633</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7880890785006347</v>
+        <v>-0.78888095504783</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.3964833403882</v>
+        <v>2.396008214459882</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.434368799665848</v>
+        <v>-5.664188194778132</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7012413737054195</v>
+        <v>0.6093136156605063</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7880890785006347</v>
+        <v>-0.78888095504783</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.402491870785126</v>
+        <v>2.402016744856808</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.286625829430846</v>
+        <v>-5.516445224543129</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8394912095914426</v>
+        <v>0.747563451546529</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.6202817212657515</v>
+        <v>-0.6210735978129468</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.582328932918077</v>
+        <v>2.58185380698976</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.388640511962067</v>
+        <v>-5.61845990707435</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8014789581104349</v>
+        <v>0.7095512000655217</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.6202817212657515</v>
+        <v>-0.6210735978129468</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.585122554449558</v>
+        <v>2.584647428521241</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.252031167867974</v>
+        <v>-5.481850562980258</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8567850441397304</v>
+        <v>0.7648572860948173</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4836723771716591</v>
+        <v>-0.4844642537188543</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.667750509297672</v>
+        <v>2.667275383369355</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.394796500690624</v>
+        <v>-5.624615895802908</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7987593877507808</v>
+        <v>0.7068316297058672</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6264377099943095</v>
+        <v>-0.6272295865415047</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.581171786344192</v>
+        <v>2.580696660415875</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.332498501914502</v>
+        <v>-5.562317897026785</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8900141410580504</v>
+        <v>0.7980863830131373</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6264377099943095</v>
+        <v>-0.6272295865415047</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.647507340141013</v>
+        <v>2.647032214212696</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.130708304249344</v>
+        <v>-5.360527699361628</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6793110925135117</v>
+        <v>0.5873833344685981</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4284195178251551</v>
+        <v>-0.4292113943723503</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.474899127831904</v>
+        <v>2.474424001903587</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.070817622606751</v>
+        <v>-5.300637017719034</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.773557597492724</v>
+        <v>0.6816298394478109</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3685288361825616</v>
+        <v>-0.3693207127297569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.581123769139635</v>
+        <v>2.580648643211318</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.168558167231725</v>
+        <v>-5.398377562344009</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7490891157587782</v>
+        <v>0.6571613577138646</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3844181143155418</v>
+        <v>-0.3852099908627371</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.586217938375891</v>
+        <v>2.585742812447573</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.344895927354655</v>
+        <v>-5.574715322466938</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6770899925342779</v>
+        <v>0.5851622344893648</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5607558744384712</v>
+        <v>-0.5615477509856664</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.478951263126805</v>
+        <v>2.478476137198487</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.344206555193431</v>
+        <v>-5.574025950305715</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6758573594386958</v>
+        <v>0.5839296013937827</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5607558744384712</v>
+        <v>-0.5615477509856664</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.477442881166733</v>
+        <v>2.476967755238416</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.350777520248024</v>
+        <v>-5.580596915360307</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6730918408522948</v>
+        <v>0.5811640828073816</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5673268394930642</v>
+        <v>-0.5681187160402594</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.473363169569414</v>
+        <v>2.472888043641096</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.342823549953252</v>
+        <v>-5.572642945065535</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6762734289702039</v>
+        <v>0.5843456709252903</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5673268394930642</v>
+        <v>-0.5681187160402594</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.473363169569414</v>
+        <v>2.472888043641096</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.332450173620165</v>
+        <v>-5.562269568732448</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6868045365312434</v>
+        <v>0.5948767784863298</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5569534631599768</v>
+        <v>-0.5577453397071721</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.485968952397071</v>
+        <v>2.485493826468753</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.204765863825869</v>
+        <v>-5.434585258938152</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7427706338236866</v>
+        <v>0.6508428757787734</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4292691533656804</v>
+        <v>-0.4300610299128756</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.567471911648374</v>
+        <v>2.566996785720056</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.265432454228257</v>
+        <v>-5.495251849340541</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7052586701386034</v>
+        <v>0.6133309120936898</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5109674700842141</v>
+        <v>-0.5117593466314093</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.505207594093125</v>
+        <v>2.504732468164808</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.200438594294612</v>
+        <v>-5.430257989406895</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7353539167226901</v>
+        <v>0.643426158677777</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4841368554800587</v>
+        <v>-0.484928732027254</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.525403665466247</v>
+        <v>2.52492853953793</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.30119723005161</v>
+        <v>-5.531016625163893</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.699211402050969</v>
+        <v>0.6072836440060554</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5729624242070641</v>
+        <v>-0.5737543007542594</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.476269263861122</v>
+        <v>2.475794137932805</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.256994392965709</v>
+        <v>-5.486813788077993</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7227721394131663</v>
+        <v>0.6308443813682527</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5287595871211637</v>
+        <v>-0.5295514636683589</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.5086705686405</v>
+        <v>2.508195442712182</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.293973420629152</v>
+        <v>-5.523792815741436</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7063905288170367</v>
+        <v>0.6144627707721235</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4917856853298331</v>
+        <v>-0.4925775618770284</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.529264910184545</v>
+        <v>2.528789784256228</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.314031499493993</v>
+        <v>-5.543850894606276</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.74961506245414</v>
+        <v>0.6576873044092268</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4917856853298331</v>
+        <v>-0.4925775618770284</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.580512675367585</v>
+        <v>2.580037549439268</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.274100826316102</v>
+        <v>-5.503920221428386</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7640280363195493</v>
+        <v>0.6721002782746361</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.4518550121519428</v>
+        <v>-0.4526468886991381</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.602911783868572</v>
+        <v>2.602436657940255</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,45 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.795333091573709</v>
+        <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.233630478753398</v>
+        <v>-5.232278255758655</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7751644035829015</v>
+        <v>0.7757052927807981</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4113846645892378</v>
+        <v>-0.1810049230294073</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.622142220644465</v>
+        <v>2.760370065580363</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="2" t="n">
+        <v>45450</v>
+      </c>
+      <c r="B1988" t="n">
+        <v>3.795274314099505</v>
+      </c>
+      <c r="C1988" t="n">
+        <v>2.960535466484028</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>-5.232278255758655</v>
+      </c>
+      <c r="E1988" t="n">
+        <v>0.7757052927807981</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>-0.1810049230294073</v>
+      </c>
+      <c r="G1988" t="n">
+        <v>2.953599263470396</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-81.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.8%</t>
+          <t>-709.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.7%</t>
+          <t>-308.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.1%</t>
+          <t>-274.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-182.5%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.975575025276293</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7268380264988168</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8305261922551981</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.619108745569963</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.34070240791504</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5800415884491494</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.126836976554211</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.440576789996387</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.749291185095718</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4153676215916371</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.194185067702739</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.02586728541155</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.299922613936765</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.189370500174199</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.442259159698548</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1313599148308433</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.187364550783077</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.758871102239196</v>
+        <v>-7.792600906165847</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01497382848326279</v>
+        <v>0.001481906912602859</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.197623241451756</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.104745924224005</v>
+        <v>-8.138475728150656</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1272765351649654</v>
+        <v>-0.1407684567356258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.193722806597451</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.268325802408389</v>
+        <v>-8.30205560633504</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1943035663837183</v>
+        <v>-0.2077954879543786</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.535425753734889</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.192127726652452</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.564987144218588</v>
+        <v>-8.598716948145238</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3091891271785894</v>
+        <v>-0.3226810487492497</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.604168889468768</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.154660821141333</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.770018324992904</v>
+        <v>-8.803748128919555</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3952279040227191</v>
+        <v>-0.4087198255933795</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.604168889468768</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.15063451660693</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.153019713735535</v>
+        <v>-9.186749517662186</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5485305608413555</v>
+        <v>-0.5620224824120159</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.604168889468768</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.150532415285346</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.33488950472057</v>
+        <v>-9.36861930864722</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6187069612639395</v>
+        <v>-0.6321988828345995</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.786038680453803</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.043982056665754</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.694419827224571</v>
+        <v>-9.728149631151222</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7571687869674899</v>
+        <v>-0.7706607085381503</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.786038680453803</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.049332359963805</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.744768890678793</v>
+        <v>-9.778498694605444</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.769392392392001</v>
+        <v>-0.7828843139626613</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.836387743908025</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.027038941848449</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.842388168100189</v>
+        <v>-9.87611797202684</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8053983527387909</v>
+        <v>-0.8188902743094508</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.934007021329421</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.97150912601738</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.989914256105832</v>
+        <v>-10.02364406003248</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8615152316194759</v>
+        <v>-0.8750071531901358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.081533109335065</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.885887029535566</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.1941724314357</v>
+        <v>-10.22790223536235</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9377053046327788</v>
+        <v>-0.9511972262034387</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.209172053949054</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.814816859885815</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.33598220564248</v>
+        <v>-10.36971200956913</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9899466598310576</v>
+        <v>-1.003438581401718</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.380450851594629</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.716532135782906</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26251237397504</v>
+        <v>-10.29624217790169</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9451870256706574</v>
+        <v>-0.9586789472413173</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.306981019927181</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.775985736276796</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.43763679136158</v>
+        <v>-10.47136659528823</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.000681571877758</v>
+        <v>-1.014173493448418</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.482105437313725</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.685466306592386</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67208888537607</v>
+        <v>-10.70581868930272</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.10168157438515</v>
+        <v>-1.11517349595581</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.482105437313725</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.67824714169079</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.95989272991331</v>
+        <v>-10.99362253383996</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.223475302974021</v>
+        <v>-1.236967224544682</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.769909281850963</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.498892644194471</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.01267888551363</v>
+        <v>-11.04640868944028</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.243473975375595</v>
+        <v>-1.256965896946256</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.86558476843336</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.44260314208359</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.13871567888192</v>
+        <v>-11.17244548280857</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.291194964093796</v>
+        <v>-1.304686885664457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.840333145623617</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.46044784439855</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.08670016491311</v>
+        <v>-11.12042996883976</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.26639842281987</v>
+        <v>-1.279890344390531</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.840333145623617</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.46443818008495</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.22837200663723</v>
+        <v>-11.26210181056388</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.32454238640826</v>
+        <v>-1.338034307978921</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.840333145623617</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.462962953186209</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.1787811622124</v>
+        <v>-11.21251096613905</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.289652638473454</v>
+        <v>-1.303144560044114</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.790742301198784</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.507770870005981</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.16597376920762</v>
+        <v>-11.19970357313427</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.297580814918228</v>
+        <v>-1.311072736488888</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.839598076207685</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.465406271353958</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.94012861648821</v>
+        <v>-10.97385842041486</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.197663680794255</v>
+        <v>-1.211155602364915</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.797671400620521</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.500141349742464</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.81554996015062</v>
+        <v>-10.84927976407727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.146693073703159</v>
+        <v>-1.160184995273819</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.797671400620521</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.501280494298523</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.8684452481949</v>
+        <v>-10.90217505212155</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.165217414758765</v>
+        <v>-1.178709336329426</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.792716054532075</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.506887476113699</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.79631207290702</v>
+        <v>-10.83004187683367</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.130630440404977</v>
+        <v>-1.144122361975637</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.792716054532075</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.512621180352335</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.72494568029738</v>
+        <v>-10.75867548422403</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.111821145754983</v>
+        <v>-1.125313067325643</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.721349661922427</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.545703753524259</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.46110881309331</v>
+        <v>-10.49483861701996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.016169880186263</v>
+        <v>-1.029661801756923</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.721349661922427</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.535820272211351</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.19386701222491</v>
+        <v>-10.44073120968211</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9111077203382769</v>
+        <v>-1.009853399321159</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.721349661922427</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.533985711711978</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.09595997354842</v>
+        <v>-10.34282417100562</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8722452198411417</v>
+        <v>-0.9709908988240241</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.65336391206187</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.574476846654851</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07200643257246</v>
+        <v>-10.31887063002966</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8619952973052647</v>
+        <v>-0.9607409762881471</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.629410371085913</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.589517477385919</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.807946494249663</v>
+        <v>-10.05481069170687</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7696316381378985</v>
+        <v>-0.86837731712078</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.365350432763117</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.734693124217844</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.100866870744825</v>
+        <v>-9.34773106820203</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4895868223962645</v>
+        <v>-0.5883325013791465</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.365350432763117</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.731906090557543</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.060682572378635</v>
+        <v>-9.30754676983584</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.473169479161947</v>
+        <v>-0.571915158144829</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.325166134396926</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.756360293465099</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.980612776840831</v>
+        <v>-9.227476974298035</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4417747397260681</v>
+        <v>-0.5405204187089501</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.245096338859122</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.803768992008539</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.747131554611233</v>
+        <v>-8.993995752068436</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3404578219963765</v>
+        <v>-0.4392035009792581</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.011615116629523</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.95178215418415</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.597465163603719</v>
+        <v>-8.844329361060922</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2834834759063303</v>
+        <v>-0.3822291548892114</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.918711625386987</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.004632038616712</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.465189689972831</v>
+        <v>-8.712053887430034</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2352057997069483</v>
+        <v>-0.3339514786898294</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.786436151756101</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.079364809542271</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.274590015299678</v>
+        <v>-8.521454212756881</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1561508691500499</v>
+        <v>-0.2548965481329315</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.595836477082948</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.1965396750338</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.025590216616097</v>
+        <v>-8.2724544140733</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.04364460845295914</v>
+        <v>-0.1423902874358403</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.595836477082948</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.209446016257459</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.131180206389201</v>
+        <v>-8.378044403846404</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2138565339614193</v>
+        <v>-0.3126022129443005</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.701426466856052</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.018116092794378</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.149915108507798</v>
+        <v>-8.396779305965001</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1728061529317717</v>
+        <v>-0.2715518319146533</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.707022476516183</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.063302828875385</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.001975067100199</v>
+        <v>-8.248839264557402</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2335090590568996</v>
+        <v>-0.3322547380397811</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.686701560607626</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.955616455732352</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.984816916968905</v>
+        <v>-8.231681114426108</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2353597852578604</v>
+        <v>-0.3341054642407415</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.669543410476332</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.95719735955765</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.941268510198214</v>
+        <v>-8.188132707655416</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2249010346446774</v>
+        <v>-0.323646713627558</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.669543410476332</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.950236747462557</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.699120116744356</v>
+        <v>-7.945984314201558</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.113579322881991</v>
+        <v>-0.2123250018648717</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.669543410476332</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.9646991018437</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.590860979621834</v>
+        <v>-7.837725177079037</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.07574354757378732</v>
+        <v>-0.174489226556668</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.669543410476332</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.959231222302895</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.467569844804704</v>
+        <v>-7.714434042261906</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02892899963635776</v>
+        <v>-0.1276746786192389</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.546252275659201</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.030703997203751</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.44642064590126</v>
+        <v>-7.693284843358462</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.01276834183765541</v>
+        <v>-0.1115140208205361</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.525103076755758</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.051094494783142</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.202655203917816</v>
+        <v>-7.449519401375018</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08051854330277308</v>
+        <v>-0.01822713568010803</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.525103076755758</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.046875203130192</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.100892383640521</v>
+        <v>-7.347756581097723</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1233479853337069</v>
+        <v>0.02460230635082628</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.511884008363329</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.056930958085665</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.851041989691447</v>
+        <v>-7.097906187148649</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.216030217897039</v>
+        <v>0.1172845389141579</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.511884008363329</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.049673033069368</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.675149897224014</v>
+        <v>-6.922014094681217</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2899861784046607</v>
+        <v>0.1912404994217796</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.511884008363329</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.053272156590016</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.50370343420155</v>
+        <v>-6.750567631658753</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3718922696682001</v>
+        <v>0.2731465906853185</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.340437545340866</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.169467540458048</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.278670434532727</v>
+        <v>-6.52553463198993</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4609259471520262</v>
+        <v>0.3621802681691451</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.115404545672043</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.303507817875639</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.215034692298793</v>
+        <v>-6.461898889755996</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4910750450999171</v>
+        <v>0.3923293661170359</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.051768803438109</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.346384064270317</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.171272510992951</v>
+        <v>-6.418136708450154</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4897741764060495</v>
+        <v>0.3910284974231684</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.051768803438109</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.327578323054112</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.930842014188091</v>
+        <v>-6.177706211645294</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5876894517528708</v>
+        <v>0.4889437727699897</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8113383066332482</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.473579697761906</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.858599446016896</v>
+        <v>-6.105463643474099</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6205157928561689</v>
+        <v>0.5217701138732878</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8113383066332482</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.477509011596726</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.805601123735508</v>
+        <v>-6.052465321192711</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.642393705686064</v>
+        <v>0.5436480267031829</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7560020476313094</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.51138935091523</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.696796238255781</v>
+        <v>-5.943660435712984</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6829137310979485</v>
+        <v>0.5841680521150674</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7560020476313094</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.508387422135223</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.476775440218771</v>
+        <v>-5.723639637675974</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7725010873233669</v>
+        <v>0.6737554083404858</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6147822025633292</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.594698366186625</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.343907751155493</v>
+        <v>-5.590771948612696</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8415423457505011</v>
+        <v>0.74279666676762</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6147822025633292</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.610592548988449</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.184392647636123</v>
+        <v>-5.431256845093326</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9064942315985509</v>
+        <v>0.8077485526156698</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4552670990439592</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.707447455540372</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.039720502536386</v>
+        <v>-5.286584699993589</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.974451192199886</v>
+        <v>0.8757055132170048</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3105949539442218</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.804338845161655</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.099595329894078</v>
+        <v>-5.346459527351281</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9365387526582349</v>
+        <v>0.8377930736753534</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3704697813019139</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.754451440148465</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.012795832115069</v>
+        <v>-5.259660029572272</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9936590450924045</v>
+        <v>0.8949133661095234</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3704697813019139</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.776851933471031</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.015265538576875</v>
+        <v>-5.262129736034078</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9927435638810942</v>
+        <v>0.8939978848982131</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3729394877637201</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77544251096736</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.083635724900885</v>
+        <v>-5.330499922358088</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.976402411826192</v>
+        <v>0.8776567328433109</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3636637887275052</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.792014852863791</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.192173905817019</v>
+        <v>-5.439038103274222</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9234238480916299</v>
+        <v>0.8246781691087488</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3636637887275052</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.782451561495682</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.223167065145724</v>
+        <v>-5.470031262602927</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7357361494005348</v>
+        <v>0.6369904704176532</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3636637887275052</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.607161126536069</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.047692805353256</v>
+        <v>-5.294557002810459</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.81049308530931</v>
+        <v>0.7117474063264289</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3636637887275052</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.611728358527857</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.158629057994505</v>
+        <v>-5.405493255451708</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7418606130140173</v>
+        <v>0.6431149340311362</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3636637887275052</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.587470387289064</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.361655635537738</v>
+        <v>-5.608519832994941</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6637813672166297</v>
+        <v>0.5650356882337486</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5666903662707385</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.468785825983029</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.203730036602445</v>
+        <v>-5.450594234059648</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.737123993222879</v>
+        <v>0.6383783142399979</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5666903662707385</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.478958212415161</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.117486573576067</v>
+        <v>-5.36435077103327</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7665676490072908</v>
+        <v>0.6678219700244092</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5666903662707385</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.473904482989022</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.162793392975047</v>
+        <v>-5.40965759043225</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7402206966922242</v>
+        <v>0.6414750177093431</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6075005292799693</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.441194160628009</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.191826497677348</v>
+        <v>-5.438690695134551</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7291593278444055</v>
+        <v>0.630413648861524</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6075005292799693</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.441746033661111</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.099016016226488</v>
+        <v>-5.345880213683691</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6955562123161148</v>
+        <v>0.5968105333332336</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.51469004782911</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.426705014422992</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.143405485555916</v>
+        <v>-5.390269683013119</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6796739005089445</v>
+        <v>0.5809282215260634</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5590795171585377</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.401944808749936</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.030734267319666</v>
+        <v>-5.277598464776869</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7198180963151679</v>
+        <v>0.6210724173322864</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4464082989222874</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.464623248203409</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.918357266136993</v>
+        <v>-5.165221463594196</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7702601926189041</v>
+        <v>0.6715145136360228</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4464082989222874</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.470114544034076</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.116591835023724</v>
+        <v>-5.363456032480927</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7024635668327508</v>
+        <v>0.6037178878498697</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.644642867809018</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.362671004470577</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.199593116049003</v>
+        <v>-5.446457313506206</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5076187744232925</v>
+        <v>0.4088730954404114</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6632137523361918</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.189884193754926</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.308207194492334</v>
+        <v>-5.555071391949537</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5843228037651658</v>
+        <v>0.4855771247822847</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6632137523361918</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.310033854474132</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.394805777473437</v>
+        <v>-5.64166997493064</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5641963966750474</v>
+        <v>0.4654507176921663</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6632137523361918</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.324546880576455</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.356422114915286</v>
+        <v>-5.603286312372489</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5769693030406766</v>
+        <v>0.4782236240577955</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6248300897780407</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.344996519453714</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.40785863836068</v>
+        <v>-5.426169982337322</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5531237225078209</v>
+        <v>0.5457991849171639</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6248300897780407</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.341725548299016</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.378156514384386</v>
+        <v>-5.396467858361029</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5656879638602512</v>
+        <v>0.5583634262695942</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.629300214993354</v>
+        <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.339726864931741</v>
+        <v>2.286334588737144</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.198781093145619</v>
+        <v>-5.217092437122261</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6312251076621727</v>
+        <v>0.6239005700715157</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4725234568226353</v>
+        <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.427579895140587</v>
+        <v>2.374187618945989</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.243795306666225</v>
+        <v>-5.262106650642867</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5940268775855198</v>
+        <v>0.5867023399948632</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5028723521372399</v>
+        <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.390178013283414</v>
+        <v>2.336785737088816</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.51079981693866</v>
+        <v>-5.529111160915302</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4929166358154915</v>
+        <v>0.485592098224835</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6972353901801884</v>
+        <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.27925175279659</v>
+        <v>2.225859476601993</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.611997598375833</v>
+        <v>-5.630308942352475</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.451641445137124</v>
+        <v>0.4443169075464675</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7656442037255076</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.2374103865659</v>
+        <v>2.184018110371303</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.579522012205061</v>
+        <v>-5.597833356181702</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4622316411597498</v>
+        <v>0.4549071035690928</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7656442037255076</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.235010348120217</v>
+        <v>2.18161807192562</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.560483884497764</v>
+        <v>-5.578795228474405</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4663716114509135</v>
+        <v>0.459047073860257</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8238278150567021</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.196624900529745</v>
+        <v>2.143232624335147</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.591610515648382</v>
+        <v>-5.609921859625024</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6315028279293466</v>
+        <v>0.6241782903386901</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8238278150567021</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.374206769468426</v>
+        <v>2.320814493273828</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.643930896249174</v>
+        <v>-5.662242240225815</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6114080046751633</v>
+        <v>0.6040834670845068</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.78888095504783</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.396008214459882</v>
+        <v>2.342615938265285</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.664188194778132</v>
+        <v>-5.682499538754773</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6093136156605063</v>
+        <v>0.6019890780698498</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.78888095504783</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.402016744856808</v>
+        <v>2.348624468662211</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.516445224543129</v>
+        <v>-5.534756568519771</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.747563451546529</v>
+        <v>0.7402389139558725</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.6210735978129468</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.58185380698976</v>
+        <v>2.528461530795163</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.61845990707435</v>
+        <v>-5.636771251050992</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7095512000655217</v>
+        <v>0.7022266624748652</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.6210735978129468</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.584647428521241</v>
+        <v>2.531255152326644</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.481850562980258</v>
+        <v>-5.500161906956899</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7648572860948173</v>
+        <v>0.7575327485041603</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4844642537188543</v>
+        <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.667275383369355</v>
+        <v>2.613883107174757</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.624615895802908</v>
+        <v>-5.642927239779549</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7068316297058672</v>
+        <v>0.6995070921152107</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6272295865415047</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.580696660415875</v>
+        <v>2.527304384221277</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.562317897026785</v>
+        <v>-5.580629241003427</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7980863830131373</v>
+        <v>0.7907618454224803</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6272295865415047</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.647032214212696</v>
+        <v>2.593639938018098</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.360527699361628</v>
+        <v>-5.378839043338269</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5873833344685981</v>
+        <v>0.5800587968779416</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4292113943723503</v>
+        <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.474424001903587</v>
+        <v>2.421031725708989</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.300637017719034</v>
+        <v>-5.318948361695676</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6816298394478109</v>
+        <v>0.6743053018571543</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3693207127297569</v>
+        <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.580648643211318</v>
+        <v>2.527256367016721</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.398377562344009</v>
+        <v>-5.41668890632065</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6571613577138646</v>
+        <v>0.6498368201232081</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3852099908627371</v>
+        <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.585742812447573</v>
+        <v>2.532350536252976</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.574715322466938</v>
+        <v>-5.593026666443579</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5851622344893648</v>
+        <v>0.5778376968987082</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5615477509856664</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.478476137198487</v>
+        <v>2.42508386100389</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.574025950305715</v>
+        <v>-5.592337294282356</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5839296013937827</v>
+        <v>0.5766050638031257</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5615477509856664</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.476967755238416</v>
+        <v>2.423575479043818</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.580596915360307</v>
+        <v>-5.598908259336949</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5811640828073816</v>
+        <v>0.5738395452167251</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5681187160402594</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.472888043641096</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.572642945065535</v>
+        <v>-5.590954289042177</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5843456709252903</v>
+        <v>0.5770211333346338</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5681187160402594</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.472888043641096</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.562269568732448</v>
+        <v>-5.58058091270909</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5948767784863298</v>
+        <v>0.5875522408956733</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5577453397071721</v>
+        <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.485493826468753</v>
+        <v>2.432101550274156</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.434585258938152</v>
+        <v>-5.452896602914794</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6508428757787734</v>
+        <v>0.6435183381881164</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4300610299128756</v>
+        <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.566996785720056</v>
+        <v>2.513604509525459</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.495251849340541</v>
+        <v>-5.513563193317182</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6133309120936898</v>
+        <v>0.6060063745030333</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5117593466314093</v>
+        <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.504732468164808</v>
+        <v>2.451340191970211</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.430257989406895</v>
+        <v>-5.448569333383537</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.643426158677777</v>
+        <v>0.63610162108712</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.484928732027254</v>
+        <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.52492853953793</v>
+        <v>2.471536263343332</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.531016625163893</v>
+        <v>-5.549327969140535</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6072836440060554</v>
+        <v>0.5999591064153988</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5737543007542594</v>
+        <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.475794137932805</v>
+        <v>2.422401861738207</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.486813788077993</v>
+        <v>-5.505125132054634</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6308443813682527</v>
+        <v>0.6235198437775962</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5295514636683589</v>
+        <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.508195442712182</v>
+        <v>2.454803166517585</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.523792815741436</v>
+        <v>-5.542104159718077</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6144627707721235</v>
+        <v>0.6071382331814665</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4925775618770284</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.528789784256228</v>
+        <v>2.475397508061631</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.543850894606276</v>
+        <v>-5.562162238582918</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6576873044092268</v>
+        <v>0.6503627668185703</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4925775618770284</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.580037549439268</v>
+        <v>2.52664527324467</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.503920221428386</v>
+        <v>-5.522231565405027</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6721002782746361</v>
+        <v>0.6647757406839796</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.4526468886991381</v>
+        <v>-0.5416340156901341</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.602436657940255</v>
+        <v>2.549044381745658</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.232278255758655</v>
+        <v>-5.481761217842323</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7757052927807981</v>
+        <v>0.6759121079473314</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1810049230294073</v>
+        <v>-0.5011636681274292</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.760370065580363</v>
+        <v>2.568274818521551</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.795274314099505</v>
+        <v>3.473057806322108</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.960535466484028</v>
+        <v>2.642351187672091</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.232278255758655</v>
+        <v>-5.481761217842323</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7757052927807981</v>
+        <v>0.6759121079473314</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1810049230294073</v>
+        <v>-0.5011636681274292</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.953599263470396</v>
+        <v>2.635414984658459</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-20.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.4%</t>
+          <t>-81.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-709.7%</t>
+          <t>-706.4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-308.6%</t>
+          <t>-307.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-157.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-274.1%</t>
+          <t>-277.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.5%</t>
+          <t>-155.3%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.340820721628761</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5799942629636607</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.248519038654257</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.367567552736359</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.74940949880944</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.4153202961061484</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.121175830442711</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.025985599125272</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2998752884512759</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.116361262914171</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.44237747341227</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1313125893453542</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.114355313523049</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.758989415952918</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>0.01492650299777409</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.124614004191728</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.104864237937727</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1273238606504545</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.120713569337423</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.268444116122112</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.1943508918692074</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.657107815834935</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.119118489392424</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.56510545793231</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.3092364526640785</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.725850951568814</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.081651583881305</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.770136638706626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.3952752295082078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.725850951568814</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.077625279346901</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.153138027449257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.5485778863268447</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.725850951568814</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.077523178025317</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.335007818434292</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.6187542867494282</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.907720742553849</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.970972819405727</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.694538140938294</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.7572161124529786</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.907720742553849</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.976323122703777</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.744887204392516</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.7694397178774901</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.958069806008071</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.954029704588421</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.842506481813912</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.8054456782242796</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.055689083429468</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.898499888757352</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-9.990032569819554</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.8615625571049645</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.203215171435111</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.812877792275538</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.19429074514942</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9377526301182675</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.3308541160491</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.741807622625787</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.33610051935621</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-0.9899939853165471</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.502132913694675</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.643522898522878</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.26263068768876</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-0.9452343511561461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.428663082027227</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.702976499016768</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.4377551050753</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-1.000728897363246</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.603787499413771</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.612457069332359</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.67220719908979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.101728899870638</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.603787499413771</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.605237904430763</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-10.96001104362703</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.22352262845951</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.891591343951009</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.425883406934444</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-11.01279719922736</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.243521300861085</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.987266830533406</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.369593904823562</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.13883399259564</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.291242289579286</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.962015207723664</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.387438607138522</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.08681847862683</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.266445748305359</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.962015207723664</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.391428942824923</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.22849032035095</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.324589711893749</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.962015207723664</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.389953715926181</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.17889947592612</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.289699963958943</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.91242436329883</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.434761632745954</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.16609208292134</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.297628140403716</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.961280138307731</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.39239703409393</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-10.94024693020193</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.197711006279744</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.919353462720567</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.427132112482437</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.81566827386434</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.146740399188648</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.919353462720567</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.428271257038496</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-10.86856356190863</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.165264740244255</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.914398116632121</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.433878238853671</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.79643038662075</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.130677765890466</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.914398116632121</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.439611943092308</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75867548422403</v>
+        <v>-10.7250639940111</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.125313067325643</v>
+        <v>-1.111868471240473</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.843031724022473</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.472694516264232</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.46122712680703</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-1.016217205671752</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.843031724022473</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.462811034951324</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.44073120968211</v>
+        <v>-10.40711971946919</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.009853399321159</v>
+        <v>-0.9964088032359881</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.843031724022473</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.46097647445195</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.34282417100562</v>
+        <v>-10.3092126807927</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9709908988240241</v>
+        <v>-0.9575463027388529</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.775045974161916</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.501467609394823</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.31887063002966</v>
+        <v>-10.28525913981674</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9607409762881471</v>
+        <v>-0.9472963802029759</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.751092433185959</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.516508240125891</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.05481069170687</v>
+        <v>-10.02119920149394</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.86837731712078</v>
+        <v>-0.8549327210356097</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.487032494863163</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.661683886957817</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.34773106820203</v>
+        <v>-9.314119577989104</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5883325013791465</v>
+        <v>-0.5748879052939757</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.487032494863163</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.658896853297516</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.30754676983584</v>
+        <v>-9.273935279622913</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.571915158144829</v>
+        <v>-0.5584705620596582</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.446848196496972</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.683351056205072</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.227476974298035</v>
+        <v>-9.193865484085109</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5405204187089501</v>
+        <v>-0.5270758226237793</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.366778400959168</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.730759754748511</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.993995752068436</v>
+        <v>-8.960384261855509</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4392035009792581</v>
+        <v>-0.4257589048940873</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.133297178729569</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.878772916924123</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.844329361060922</v>
+        <v>-8.810717870847995</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3822291548892114</v>
+        <v>-0.3687845588040406</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-2.040393687487033</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>1.931622801356685</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.712053887430034</v>
+        <v>-8.678442397217108</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3339514786898294</v>
+        <v>-0.3205068826046586</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.908118213856146</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.006355572282244</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.521454212756881</v>
+        <v>-8.487842722543954</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2548965481329315</v>
+        <v>-0.2414519520477607</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.717518539182993</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.123530437773772</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.2724544140733</v>
+        <v>-8.238842923860373</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1423902874358403</v>
+        <v>-0.1289456913506695</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.717518539182993</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.136436778997432</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.378044403846404</v>
+        <v>-8.344432913633478</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3126022129443005</v>
+        <v>-0.2991576168591301</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.823108528956098</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>1.94510685553435</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.396779305965001</v>
+        <v>-8.363167815752075</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2715518319146533</v>
+        <v>-0.2581072358294825</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.828704538616229</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>1.990293591615358</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.248839264557402</v>
+        <v>-8.215227774344475</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3322547380397811</v>
+        <v>-0.3188101419546103</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.808383622707672</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.882607218472325</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.231681114426108</v>
+        <v>-8.198069624213181</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3341054642407415</v>
+        <v>-0.3206608681555707</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.791225472576377</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.884188122297623</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.188132707655416</v>
+        <v>-8.15452121744249</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.323646713627558</v>
+        <v>-0.3102021175423872</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.791225472576377</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.87722751020253</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.945984314201558</v>
+        <v>-7.912372823988632</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2123250018648717</v>
+        <v>-0.1988804057797009</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.791225472576377</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.891689864583673</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.837725177079037</v>
+        <v>-7.80411368686611</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.174489226556668</v>
+        <v>-0.1610446304714972</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.791225472576377</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.886221985042868</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.714434042261906</v>
+        <v>-7.680822552048979</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1276746786192389</v>
+        <v>-0.1142300825340681</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.667934337759247</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>1.957694759943723</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.693284843358462</v>
+        <v>-7.659673353145536</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1115140208205361</v>
+        <v>-0.09806942473536573</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.646785138855803</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>1.978085257523114</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.449519401375018</v>
+        <v>-7.415907911162091</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01822713568010803</v>
+        <v>-0.004782539594937241</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.646785138855803</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>1.973865965870165</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.347756581097723</v>
+        <v>-7.314145090884796</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.02460230635082628</v>
+        <v>0.03804690243599662</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.633566070463375</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>1.983921720825638</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.097906187148649</v>
+        <v>-7.064294696935722</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1172845389141579</v>
+        <v>0.1307291349993287</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.633566070463375</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>1.97666379580934</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.922014094681217</v>
+        <v>-6.88840260446829</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1912404994217796</v>
+        <v>0.2046850955069504</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.633566070463375</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>1.980262919329989</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.750567631658753</v>
+        <v>-6.716956141445826</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2731465906853185</v>
+        <v>0.2865911867704893</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.462119607440911</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.096458303198021</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.52553463198993</v>
+        <v>-6.491923141777003</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3621802681691451</v>
+        <v>0.3756248642543154</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.237086607772088</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.230498580615611</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883077</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.461898889755996</v>
+        <v>-6.428287399543069</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3923293661170359</v>
+        <v>0.4057739622022067</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.173450865538154</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.27337482701029</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.418136708450154</v>
+        <v>-6.384525218237227</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3910284974231684</v>
+        <v>0.4044730935083387</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.173450865538154</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.254569085794085</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242297</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.177706211645294</v>
+        <v>-6.144094721432367</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4889437727699897</v>
+        <v>0.5023883688551605</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9330203687332936</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.400570460501879</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.105463643474099</v>
+        <v>-6.071852153261172</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5217701138732878</v>
+        <v>0.5352147099584585</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9330203687332936</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.404499774336699</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.052465321192711</v>
+        <v>-6.018853830979785</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5436480267031829</v>
+        <v>0.5570926227883537</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8776841097313548</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.438380113655202</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.943660435712984</v>
+        <v>-5.910048945500058</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.5841680521150674</v>
+        <v>0.5976126482002382</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8776841097313548</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.435378184875196</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.723639637675974</v>
+        <v>-5.690028147463047</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.6737554083404858</v>
+        <v>0.6872000044256565</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7364642646633746</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.521689128926598</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.590771948612696</v>
+        <v>-5.557160458399769</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.74279666676762</v>
+        <v>0.7562412628527908</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7364642646633746</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.537583311728421</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.431256845093326</v>
+        <v>-5.3976453548804</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8077485526156698</v>
+        <v>0.8211931487008406</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.5769491611440046</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.634438218280345</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.286584699993589</v>
+        <v>-5.252973209780662</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.8757055132170048</v>
+        <v>0.8891501093021752</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.4322770160442672</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.731329607901627</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.346459527351281</v>
+        <v>-5.312848037138354</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8377930736753534</v>
+        <v>0.8512376697605242</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.4921518434019593</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.681442202888438</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.259660029572272</v>
+        <v>-5.226048539359345</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.8949133661095234</v>
+        <v>0.9083579621946942</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.4921518434019593</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.703842696211004</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.262129736034078</v>
+        <v>-5.228518245821151</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.8939978848982131</v>
+        <v>0.9074424809833839</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.4946215498637655</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.702433273707332</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.330499922358088</v>
+        <v>-5.296888432145161</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8776567328433109</v>
+        <v>0.8911013289284817</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4853458508275506</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.719005615603764</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.439038103274222</v>
+        <v>-5.405426613061295</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8246781691087488</v>
+        <v>0.8381227651939196</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4853458508275506</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.709442324235655</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.470031262602927</v>
+        <v>-5.436419772390001</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.6369904704176532</v>
+        <v>0.650435066502824</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4853458508275506</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.534151889276042</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.294557002810459</v>
+        <v>-5.260945512597532</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7117474063264289</v>
+        <v>0.7251920024115992</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4853458508275506</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.53871912126783</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.405493255451708</v>
+        <v>-5.371881765238781</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6431149340311362</v>
+        <v>0.656559530116307</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4853458508275506</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.514461150029037</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.608519832994941</v>
+        <v>-5.574908342782014</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.5650356882337486</v>
+        <v>0.578480284318919</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6883724283707839</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.395776588723002</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.450594234059648</v>
+        <v>-5.416982743846721</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6383783142399979</v>
+        <v>0.6518229103251687</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6883724283707839</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.405948975155134</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.36435077103327</v>
+        <v>-5.330739280820343</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.6678219700244092</v>
+        <v>0.68126656610958</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6883724283707839</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.400895245728995</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.40965759043225</v>
+        <v>-5.376046100219323</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6414750177093431</v>
+        <v>0.6549196137945139</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7291825913800147</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.368184923367981</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.438690695134551</v>
+        <v>-5.405079204921624</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.630413648861524</v>
+        <v>0.6438582449466947</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7291825913800147</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.368736796401083</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.345880213683691</v>
+        <v>-5.312268723470765</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.5968105333332336</v>
+        <v>0.6102551294184044</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.6363721099291554</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.353695777162964</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.390269683013119</v>
+        <v>-5.356658192800192</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.5809282215260634</v>
+        <v>0.5943728176112342</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.680761579258583</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.328935571489909</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.277598464776869</v>
+        <v>-5.243986974563942</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6210724173322864</v>
+        <v>0.6345170134174571</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5680903610223329</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.391614010943382</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.165221463594196</v>
+        <v>-5.131609973381269</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.6715145136360228</v>
+        <v>0.6849591097211936</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5680903610223329</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.397105306774049</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.363456032480927</v>
+        <v>-5.329844542268</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6037178878498697</v>
+        <v>0.6171624839350405</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.7663249299090635</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.28966176721055</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.446457313506206</v>
+        <v>-5.412845823293279</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4088730954404114</v>
+        <v>0.4223176915255822</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7848958144362372</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.116874956494899</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.555071391949537</v>
+        <v>-5.52145990173661</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.4855771247822847</v>
+        <v>0.4990217208674554</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7848958144362372</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.237024617214105</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.64166997493064</v>
+        <v>-5.608058484717713</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.4654507176921663</v>
+        <v>0.4788953137773371</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7848958144362372</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.251537643316428</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.603286312372489</v>
+        <v>-5.569674822159562</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.4782236240577955</v>
+        <v>0.4916682201429663</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.7465121518780861</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.271987282193687</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.426169982337322</v>
+        <v>-5.392558492124396</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5457991849171639</v>
+        <v>0.5592437810023347</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.7465121518780861</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.268716311038989</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.396467858361029</v>
+        <v>-5.362856368148102</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5583634262695942</v>
+        <v>0.571808022354765</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7182873419843501</v>
+        <v>-0.7509822770933994</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.286334588737144</v>
+        <v>2.266717627671714</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.217092437122261</v>
+        <v>-5.183480946909334</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6239005700715157</v>
+        <v>0.6373451661566865</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5615105838136314</v>
+        <v>-0.5942055189226807</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.374187618945989</v>
+        <v>2.35457065788056</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.262106650642867</v>
+        <v>-5.22849516042994</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5867023399948632</v>
+        <v>0.600146936080034</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.591859479128236</v>
+        <v>-0.6245544142372853</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336785737088816</v>
+        <v>2.317168776023387</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.529111160915302</v>
+        <v>-5.495499670702375</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.485592098224835</v>
+        <v>0.4990366943100057</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7862225171711845</v>
+        <v>-0.8189174522802338</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225859476601993</v>
+        <v>2.206242515536563</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.630308942352475</v>
+        <v>-5.596697452139548</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4443169075464675</v>
+        <v>0.4577615036316383</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.887326265825553</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.184018110371303</v>
+        <v>2.164401149305873</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.597833356181702</v>
+        <v>-5.564221865968776</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4549071035690928</v>
+        <v>0.4683516996542636</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.887326265825553</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.18161807192562</v>
+        <v>2.16200111086019</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.578795228474405</v>
+        <v>-5.545183738261478</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.459047073860257</v>
+        <v>0.4724916699454274</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9455098771567475</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.143232624335147</v>
+        <v>2.123615663269718</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.609921859625024</v>
+        <v>-5.576310369412097</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6241782903386901</v>
+        <v>0.6376228864238609</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9455098771567475</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320814493273828</v>
+        <v>2.301197532208398</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.662242240225815</v>
+        <v>-5.628630750012888</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6040834670845068</v>
+        <v>0.6175280631696776</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9105630171478754</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.342615938265285</v>
+        <v>2.322998977199855</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.682499538754773</v>
+        <v>-5.648888048541846</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6019890780698498</v>
+        <v>0.6154336741550201</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9105630171478754</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.348624468662211</v>
+        <v>2.329007507596781</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.534756568519771</v>
+        <v>-5.501145078306844</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7402389139558725</v>
+        <v>0.7536835100410433</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.7427556599129922</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.528461530795163</v>
+        <v>2.508844569729733</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.636771251050992</v>
+        <v>-5.603159760838065</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7022266624748652</v>
+        <v>0.7156712585600356</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.7427556599129922</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.531255152326644</v>
+        <v>2.511638191261214</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.500161906956899</v>
+        <v>-5.466550416743972</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7575327485041603</v>
+        <v>0.7709773445893311</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5734513807098505</v>
+        <v>-0.6061463158188998</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613883107174757</v>
+        <v>2.594266146109328</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.642927239779549</v>
+        <v>-5.609315749566623</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6995070921152107</v>
+        <v>0.7129516882003815</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.7489116486415501</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.527304384221277</v>
+        <v>2.507687423155848</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.580629241003427</v>
+        <v>-5.5470177507905</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7907618454224803</v>
+        <v>0.8042064415076511</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.7489116486415501</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.593639938018098</v>
+        <v>2.574022976952669</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.378839043338269</v>
+        <v>-5.345227553125342</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5800587968779416</v>
+        <v>0.5935033929631124</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5181985213633464</v>
+        <v>-0.5508934564723957</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.40141476464356</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.318948361695676</v>
+        <v>-5.285336871482749</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6743053018571543</v>
+        <v>0.6877498979423251</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.458307839720753</v>
+        <v>-0.4910027748298023</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.507639405951291</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.41668890632065</v>
+        <v>-5.383077416107724</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6498368201232081</v>
+        <v>0.6632814162083789</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4741971178537331</v>
+        <v>-0.5068920529627825</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.512733575187546</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.593026666443579</v>
+        <v>-5.559415176230653</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5778376968987082</v>
+        <v>0.5912822929838786</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.683229813085712</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.40546689993846</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.592337294282356</v>
+        <v>-5.55872580406943</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5766050638031257</v>
+        <v>0.5900496598882965</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.683229813085712</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.403958517978389</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.598908259336949</v>
+        <v>-5.565296769124022</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5738395452167251</v>
+        <v>0.5872841413018959</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.6898007781403049</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.399878806381069</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.590954289042177</v>
+        <v>-5.55734279882925</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5770211333346338</v>
+        <v>0.5904657294198046</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.6898007781403049</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.399878806381069</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.58058091270909</v>
+        <v>-5.546969422496163</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5875522408956733</v>
+        <v>0.6009968369808441</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6467324666981682</v>
+        <v>-0.6794274018072176</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.412484589208726</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.452896602914794</v>
+        <v>-5.419285112701867</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6435183381881164</v>
+        <v>0.6569629342732872</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5190481569038717</v>
+        <v>-0.5517430920129212</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.493987548460029</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.513563193317182</v>
+        <v>-5.479951703104256</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6060063745030333</v>
+        <v>0.6194509705882041</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6007464736224054</v>
+        <v>-0.6334414087314548</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.431723230904781</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.448569333383537</v>
+        <v>-5.41495784317061</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.63610162108712</v>
+        <v>0.6495462171722908</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.57391585901825</v>
+        <v>-0.6066107941272995</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.451919302277903</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.549327969140535</v>
+        <v>-5.515716478927608</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5999591064153988</v>
+        <v>0.6134037025005696</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6627414277452555</v>
+        <v>-0.6954363628543049</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.402784900672778</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.505125132054634</v>
+        <v>-5.471513641841708</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6235198437775962</v>
+        <v>0.636964439862767</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.618538590659355</v>
+        <v>-0.6512335257684044</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.435186205452155</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.542104159718077</v>
+        <v>-5.50849266950515</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6071382331814665</v>
+        <v>0.6205828292666373</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.6142596239770739</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.475397508061631</v>
+        <v>2.455780546996201</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.562162238582918</v>
+        <v>-5.528550748369991</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6503627668185703</v>
+        <v>0.6638073629037406</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.6142596239770739</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.52664527324467</v>
+        <v>2.507028312179241</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.522231565405027</v>
+        <v>-5.488620075192101</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6647757406839796</v>
+        <v>0.6782203367691499</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5416340156901341</v>
+        <v>-0.5743289507991836</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.549044381745658</v>
+        <v>2.529427420680228</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.481761217842323</v>
+        <v>-5.448149727629396</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6759121079473314</v>
+        <v>0.6893567040325022</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5011636681274292</v>
+        <v>-0.5338586032364786</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.568274818521551</v>
+        <v>2.548657857456121</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.473057806322108</v>
+        <v>3.829275871227025</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.642351187672091</v>
+        <v>2.914549116875255</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.481761217842323</v>
+        <v>-5.448149727629396</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.6759121079473314</v>
+        <v>0.6893567040325022</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.5011636681274292</v>
+        <v>-0.5338586032364786</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.635414984658459</v>
+        <v>2.907612913861623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-23.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-80.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>449.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-706.4%</t>
+          <t>-692.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-307.3%</t>
+          <t>-299.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-189.7%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.340820721628761</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5799942629636607</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.248519038654257</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.367567552736359</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.74940949880944</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4153202961061484</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.121175830442711</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.025985599125272</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2998752884512759</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.116361262914171</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.44237747341227</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1313125893453542</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.114355313523049</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.758989415952918</v>
+        <v>-7.792600906165847</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01492650299777409</v>
+        <v>0.001481906912602859</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.124614004191728</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.104864237937727</v>
+        <v>-8.138475728150656</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1273238606504545</v>
+        <v>-0.1407684567356258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.120713569337423</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.268444116122112</v>
+        <v>-8.30205560633504</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1943508918692074</v>
+        <v>-0.2077954879543786</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.657107815834935</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.119118489392424</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.56510545793231</v>
+        <v>-8.598716948145238</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3092364526640785</v>
+        <v>-0.3226810487492497</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.725850951568814</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.081651583881305</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.770136638706626</v>
+        <v>-8.803748128919555</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3952752295082078</v>
+        <v>-0.4087198255933795</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.725850951568814</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.077625279346901</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.153138027449257</v>
+        <v>-9.186749517662186</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5485778863268447</v>
+        <v>-0.5620224824120159</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.725850951568814</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.077523178025317</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.335007818434292</v>
+        <v>-9.36861930864722</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6187542867494282</v>
+        <v>-0.6321988828345995</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.907720742553849</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.970972819405727</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.694538140938294</v>
+        <v>-9.728149631151222</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7572161124529786</v>
+        <v>-0.7706607085381503</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.907720742553849</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.976323122703777</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.744887204392516</v>
+        <v>-9.778498694605444</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7694397178774901</v>
+        <v>-0.7828843139626613</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.958069806008071</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.954029704588421</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.842506481813912</v>
+        <v>-9.87611797202684</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8054456782242796</v>
+        <v>-0.8188902743094508</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.055689083429468</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.898499888757352</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.990032569819554</v>
+        <v>-10.02364406003248</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8615625571049645</v>
+        <v>-0.8750071531901358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.203215171435111</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.812877792275538</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.19429074514942</v>
+        <v>-10.22790223536235</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9377526301182675</v>
+        <v>-0.9511972262034387</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.3308541160491</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.741807622625787</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.33610051935621</v>
+        <v>-10.36971200956913</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9899939853165471</v>
+        <v>-1.003438581401718</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.502132913694675</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.643522898522878</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26263068768876</v>
+        <v>-10.29624217790169</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9452343511561461</v>
+        <v>-0.9586789472413173</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.428663082027227</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.702976499016768</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.4377551050753</v>
+        <v>-10.47136659528823</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.000728897363246</v>
+        <v>-1.014173493448418</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.603787499413771</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.612457069332359</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67220719908979</v>
+        <v>-10.70581868930272</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.101728899870638</v>
+        <v>-1.11517349595581</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.603787499413771</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.605237904430763</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.96001104362703</v>
+        <v>-10.99362253383996</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.22352262845951</v>
+        <v>-1.236967224544682</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.891591343951009</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.425883406934444</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.01279719922736</v>
+        <v>-11.04640868944028</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.243521300861085</v>
+        <v>-1.256965896946256</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.987266830533406</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.369593904823562</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.13883399259564</v>
+        <v>-11.17244548280857</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.291242289579286</v>
+        <v>-1.304686885664457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.962015207723664</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.387438607138522</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.08681847862683</v>
+        <v>-11.12042996883976</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.266445748305359</v>
+        <v>-1.279890344390531</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.962015207723664</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.391428942824923</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.22849032035095</v>
+        <v>-11.26210181056388</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.324589711893749</v>
+        <v>-1.338034307978921</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.962015207723664</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.389953715926181</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.17889947592612</v>
+        <v>-11.21251096613905</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.289699963958943</v>
+        <v>-1.303144560044114</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.91242436329883</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.434761632745954</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.16609208292134</v>
+        <v>-11.19970357313427</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.297628140403716</v>
+        <v>-1.311072736488888</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.961280138307731</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.39239703409393</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.94024693020193</v>
+        <v>-10.97385842041486</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.197711006279744</v>
+        <v>-1.211155602364915</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.919353462720567</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.427132112482437</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.81566827386434</v>
+        <v>-10.84927976407727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.146740399188648</v>
+        <v>-1.160184995273819</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.919353462720567</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.428271257038496</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.86856356190863</v>
+        <v>-10.90217505212155</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.165264740244255</v>
+        <v>-1.178709336329426</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.914398116632121</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.433878238853671</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.79643038662075</v>
+        <v>-10.83004187683367</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.130677765890466</v>
+        <v>-1.144122361975637</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.914398116632121</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.439611943092308</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.7250639940111</v>
+        <v>-10.75867548422403</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.111868471240473</v>
+        <v>-1.125313067325643</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.843031724022473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.472694516264232</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.46122712680703</v>
+        <v>-10.49483861701996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.016217205671752</v>
+        <v>-1.029661801756923</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.843031724022473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.462811034951324</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.40711971946919</v>
+        <v>-10.22759681615156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9964088032359881</v>
+        <v>-0.9245996419089377</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.843031724022473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.46097647445195</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.3092126807927</v>
+        <v>-10.12968977747507</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9575463027388529</v>
+        <v>-0.8857371414118025</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.775045974161916</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.501467609394823</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.28525913981674</v>
+        <v>-10.10573623649911</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9472963802029759</v>
+        <v>-0.8754872188759255</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.751092433185959</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.516508240125891</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.02119920149394</v>
+        <v>-9.841676298176314</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8549327210356097</v>
+        <v>-0.7831235597085588</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.487032494863163</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.661683886957817</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.314119577989104</v>
+        <v>-9.134596674671476</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5748879052939757</v>
+        <v>-0.5030787439669249</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.487032494863163</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.658896853297516</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.273935279622913</v>
+        <v>-9.094412376305286</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5584705620596582</v>
+        <v>-0.4866614007326073</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.446848196496972</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.683351056205072</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.193865484085109</v>
+        <v>-9.014342580767481</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5270758226237793</v>
+        <v>-0.4552666612967284</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.366778400959168</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.730759754748511</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.960384261855509</v>
+        <v>-8.780861358537884</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4257589048940873</v>
+        <v>-0.3539497435670369</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.133297178729569</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.878772916924123</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.810717870847995</v>
+        <v>-8.631194967530369</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3687845588040406</v>
+        <v>-0.2969753974769906</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.040393687487033</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.931622801356685</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.678442397217108</v>
+        <v>-8.498919493899482</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3205068826046586</v>
+        <v>-0.2486977212776087</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.908118213856146</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.006355572282244</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.487842722543954</v>
+        <v>-8.308319819226329</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2414519520477607</v>
+        <v>-0.1696427907207103</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.717518539182993</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.123530437773772</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.238842923860373</v>
+        <v>-8.059320020542748</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1289456913506695</v>
+        <v>-0.05713653002361907</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.717518539182993</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.136436778997432</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.344432913633478</v>
+        <v>-8.164910010315852</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2991576168591301</v>
+        <v>-0.2273484555320797</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.823108528956098</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.94510685553435</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.363167815752075</v>
+        <v>-8.183644912434449</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2581072358294825</v>
+        <v>-0.1862980745024321</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.828704538616229</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.990293591615358</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.215227774344475</v>
+        <v>-8.03570487102685</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3188101419546103</v>
+        <v>-0.2470009806275599</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.808383622707672</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.882607218472325</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.198069624213181</v>
+        <v>-8.018546720895555</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3206608681555707</v>
+        <v>-0.2488517068285203</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.791225472576377</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.884188122297623</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.15452121744249</v>
+        <v>-7.974998314124865</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3102021175423872</v>
+        <v>-0.2383929562153373</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.791225472576377</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.87722751020253</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.912372823988632</v>
+        <v>-7.732849920671007</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1988804057797009</v>
+        <v>-0.1270712444526509</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.791225472576377</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.891689864583673</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.80411368686611</v>
+        <v>-7.624590783548485</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1610446304714972</v>
+        <v>-0.08923546914444724</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.791225472576377</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.886221985042868</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.680822552048979</v>
+        <v>-7.501299648731354</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1142300825340681</v>
+        <v>-0.04242092120701813</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.667934337759247</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.957694759943723</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.659673353145536</v>
+        <v>-7.480150449827911</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.09806942473536573</v>
+        <v>-0.02626026340831578</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.646785138855803</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.978085257523114</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.415907911162091</v>
+        <v>-7.236385007844467</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.004782539594937241</v>
+        <v>0.06702662173211271</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.646785138855803</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.973865965870165</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.314145090884796</v>
+        <v>-7.134622187567172</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03804690243599662</v>
+        <v>0.1098560637630466</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.633566070463375</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.983921720825638</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.064294696935722</v>
+        <v>-6.884771793618097</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1307291349993287</v>
+        <v>0.2025382963263787</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.633566070463375</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.97666379580934</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.88840260446829</v>
+        <v>-6.708879701150664</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2046850955069504</v>
+        <v>0.2764942568340008</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.633566070463375</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.980262919329989</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.716956141445826</v>
+        <v>-6.537433238128201</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2865911867704893</v>
+        <v>0.3584003480975397</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.462119607440911</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.096458303198021</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.491923141777003</v>
+        <v>-6.312400238459378</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3756248642543154</v>
+        <v>0.4474340255813658</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.237086607772088</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.230498580615611</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.428287399543069</v>
+        <v>-6.248764496225443</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4057739622022067</v>
+        <v>0.4775831235292567</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.173450865538154</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.27337482701029</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.384525218237227</v>
+        <v>-6.205002314919602</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4044730935083387</v>
+        <v>0.4762822548353891</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.173450865538154</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.254569085794085</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.144094721432367</v>
+        <v>-6.171893021314886</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5023883688551605</v>
+        <v>0.4912690489021529</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9330203687332936</v>
+        <v>-1.107646636824389</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.400570460501879</v>
+        <v>2.295794699647222</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.071852153261172</v>
+        <v>-6.099650453143691</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5352147099584585</v>
+        <v>0.524095390005451</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9330203687332936</v>
+        <v>-1.107646636824389</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.404499774336699</v>
+        <v>2.299724013482042</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.018853830979785</v>
+        <v>-6.046652130862303</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5570926227883537</v>
+        <v>0.5459733028353462</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8776841097313548</v>
+        <v>-1.05231037782245</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.438380113655202</v>
+        <v>2.333604352800545</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.910048945500058</v>
+        <v>-5.937847245382576</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.5976126482002382</v>
+        <v>0.5864933282472307</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8776841097313548</v>
+        <v>-1.05231037782245</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.435378184875196</v>
+        <v>2.330602424020539</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.690028147463047</v>
+        <v>-5.717826447345566</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.6872000044256565</v>
+        <v>0.676080684472649</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7364642646633746</v>
+        <v>-0.9110905327544698</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.521689128926598</v>
+        <v>2.416913368071941</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.557160458399769</v>
+        <v>-5.584958758282288</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7562412628527908</v>
+        <v>0.7451219428997833</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7364642646633746</v>
+        <v>-0.9110905327544698</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.537583311728421</v>
+        <v>2.432807550873764</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.3976453548804</v>
+        <v>-5.425443654762918</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8211931487008406</v>
+        <v>0.8100738287478331</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5769491611440046</v>
+        <v>-0.7515754292350999</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.634438218280345</v>
+        <v>2.529662457425688</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.252973209780662</v>
+        <v>-5.280771509663181</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.8891501093021752</v>
+        <v>0.8780307893491681</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4322770160442672</v>
+        <v>-0.6069032841353625</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.731329607901627</v>
+        <v>2.62655384704697</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.312848037138354</v>
+        <v>-5.340646337020873</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8512376697605242</v>
+        <v>0.8401183498075167</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4921518434019593</v>
+        <v>-0.6667781114930547</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.681442202888438</v>
+        <v>2.576666442033781</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.226048539359345</v>
+        <v>-5.253846839241865</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9083579621946942</v>
+        <v>0.8972386422416863</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4921518434019593</v>
+        <v>-0.6667781114930547</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.703842696211004</v>
+        <v>2.599066935356347</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.228518245821151</v>
+        <v>-5.256316545703671</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9074424809833839</v>
+        <v>0.8963231610303759</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4946215498637655</v>
+        <v>-0.6692478179548609</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.702433273707332</v>
+        <v>2.597657512852675</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.296888432145161</v>
+        <v>-5.324686732027681</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8911013289284817</v>
+        <v>0.8799820089754737</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4853458508275506</v>
+        <v>-0.6599721189186459</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.719005615603764</v>
+        <v>2.614229854749107</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.405426613061295</v>
+        <v>-5.433224912943815</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8381227651939196</v>
+        <v>0.8270034452409116</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4853458508275506</v>
+        <v>-0.6599721189186459</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.709442324235655</v>
+        <v>2.604666563380998</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.436419772390001</v>
+        <v>-5.46421807227252</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.650435066502824</v>
+        <v>0.6393157465498165</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4853458508275506</v>
+        <v>-0.6599721189186459</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.534151889276042</v>
+        <v>2.429376128421385</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.260945512597532</v>
+        <v>-5.288743812480051</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7251920024115992</v>
+        <v>0.7140726824585917</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4853458508275506</v>
+        <v>-0.6599721189186459</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.53871912126783</v>
+        <v>2.433943360413172</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.371881765238781</v>
+        <v>-5.3996800651213</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.656559530116307</v>
+        <v>0.645440210163299</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4853458508275506</v>
+        <v>-0.6599721189186459</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.514461150029037</v>
+        <v>2.409685389174379</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.574908342782014</v>
+        <v>-5.602706642664534</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.578480284318919</v>
+        <v>0.5673609643659114</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6883724283707839</v>
+        <v>-0.8629986964618793</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.395776588723002</v>
+        <v>2.291000827868345</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.416982743846721</v>
+        <v>-5.444781043729241</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6518229103251687</v>
+        <v>0.6407035903721607</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6883724283707839</v>
+        <v>-0.8629986964618793</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.405948975155134</v>
+        <v>2.301173214300477</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.330739280820343</v>
+        <v>-5.358537580702863</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.68126656610958</v>
+        <v>0.6701472461565725</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6883724283707839</v>
+        <v>-0.8629986964618793</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.400895245728995</v>
+        <v>2.296119484874338</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.376046100219323</v>
+        <v>-5.403844400101843</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6549196137945139</v>
+        <v>0.6438002938415059</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7291825913800147</v>
+        <v>-0.9038088594711101</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.368184923367981</v>
+        <v>2.263409162513325</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.405079204921624</v>
+        <v>-5.432877504804144</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6438582449466947</v>
+        <v>0.6327389249936872</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7291825913800147</v>
+        <v>-0.9038088594711101</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.368736796401083</v>
+        <v>2.263961035546426</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.312268723470765</v>
+        <v>-5.340067023353284</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6102551294184044</v>
+        <v>0.5991358094653965</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6363721099291554</v>
+        <v>-0.8109983780202508</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.353695777162964</v>
+        <v>2.248920016308308</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.356658192800192</v>
+        <v>-5.384456492682712</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.5943728176112342</v>
+        <v>0.5832534976582262</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.680761579258583</v>
+        <v>-0.8553878473496784</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.328935571489909</v>
+        <v>2.224159810635252</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.243986974563942</v>
+        <v>-5.271785274446462</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6345170134174571</v>
+        <v>0.6233976934644496</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5680903610223329</v>
+        <v>-0.7427166291134282</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.391614010943382</v>
+        <v>2.286838250088725</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.131609973381269</v>
+        <v>-5.159408273263788</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.6849591097211936</v>
+        <v>0.673839789768186</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5680903610223329</v>
+        <v>-0.7427166291134282</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.397105306774049</v>
+        <v>2.292329545919392</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.329844542268</v>
+        <v>-5.357642842150519</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6171624839350405</v>
+        <v>0.6060431639820325</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7663249299090635</v>
+        <v>-0.9409511980001588</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.28966176721055</v>
+        <v>2.184886006355893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.412845823293279</v>
+        <v>-5.440644123175798</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4223176915255822</v>
+        <v>0.4111983715725742</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7848958144362372</v>
+        <v>-0.9595220825273325</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.116874956494899</v>
+        <v>2.012099195640242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.52145990173661</v>
+        <v>-5.549258201619129</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.4990217208674554</v>
+        <v>0.4879024009144475</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7848958144362372</v>
+        <v>-0.9595220825273325</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.237024617214105</v>
+        <v>2.132248856359447</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.608058484717713</v>
+        <v>-5.635856784600232</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.4788953137773371</v>
+        <v>0.4677759938243291</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7848958144362372</v>
+        <v>-0.9595220825273325</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.251537643316428</v>
+        <v>2.14676188246177</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.569674822159562</v>
+        <v>-5.597473122042081</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.4916682201429663</v>
+        <v>0.4805489001899583</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7465121518780861</v>
+        <v>-0.9211384199691813</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.271987282193687</v>
+        <v>2.16721152133903</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.392558492124396</v>
+        <v>-5.420356792006915</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5592437810023347</v>
+        <v>0.5481244610493268</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7465121518780861</v>
+        <v>-0.9211384199691813</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.268716311038989</v>
+        <v>2.163940550184332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.362856368148102</v>
+        <v>-5.390654668030622</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.571808022354765</v>
+        <v>0.5606887024017575</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7509822770933994</v>
+        <v>-0.9256085451844946</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.266717627671714</v>
+        <v>2.161941866817057</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.183480946909334</v>
+        <v>-5.211279246791854</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6373451661566865</v>
+        <v>0.6262258462036789</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5942055189226807</v>
+        <v>-0.768831787013776</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.35457065788056</v>
+        <v>2.249794897025903</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.22849516042994</v>
+        <v>-5.25629346031246</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.600146936080034</v>
+        <v>0.589027616127026</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6245544142372853</v>
+        <v>-0.7991806823283806</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.317168776023387</v>
+        <v>2.212393015168729</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.495499670702375</v>
+        <v>-5.523297970584895</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4990366943100057</v>
+        <v>0.4879173743569978</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8189174522802338</v>
+        <v>-0.9935437203713291</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.206242515536563</v>
+        <v>2.101466754681906</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.596697452139548</v>
+        <v>-5.624495752022067</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4577615036316383</v>
+        <v>0.4466421836786303</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.887326265825553</v>
+        <v>-1.061952533916648</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.164401149305873</v>
+        <v>2.059625388451216</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.564221865968776</v>
+        <v>-5.592020165851295</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4683516996542636</v>
+        <v>0.4572323797012561</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.887326265825553</v>
+        <v>-1.061952533916648</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.16200111086019</v>
+        <v>2.057225350005533</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.545183738261478</v>
+        <v>-5.572982038143998</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4724916699454274</v>
+        <v>0.4613723499924198</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9455098771567475</v>
+        <v>-1.120136145247843</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.123615663269718</v>
+        <v>2.018839902415061</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.576310369412097</v>
+        <v>-5.604108669294616</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6376228864238609</v>
+        <v>0.6265035664708529</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9455098771567475</v>
+        <v>-1.120136145247843</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.301197532208398</v>
+        <v>2.196421771353741</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.628630750012888</v>
+        <v>-5.656429049895408</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6175280631696776</v>
+        <v>0.6064087432166696</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9105630171478754</v>
+        <v>-1.085189285238971</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.322998977199855</v>
+        <v>2.218223216345198</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.648888048541846</v>
+        <v>-5.676686348424366</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6154336741550201</v>
+        <v>0.6043143542020126</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9105630171478754</v>
+        <v>-1.085189285238971</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.329007507596781</v>
+        <v>2.224231746742124</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.501145078306844</v>
+        <v>-5.528943378189363</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7536835100410433</v>
+        <v>0.7425641900880353</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7427556599129922</v>
+        <v>-0.9173819280040875</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.508844569729733</v>
+        <v>2.404068808875076</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.603159760838065</v>
+        <v>-5.630958060720585</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7156712585600356</v>
+        <v>0.704551938607028</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7427556599129922</v>
+        <v>-0.9173819280040875</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.511638191261214</v>
+        <v>2.406862430406557</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.466550416743972</v>
+        <v>-5.494348716626492</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7709773445893311</v>
+        <v>0.7598580246363236</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6061463158188998</v>
+        <v>-0.780772583909995</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.594266146109328</v>
+        <v>2.489490385254671</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.609315749566623</v>
+        <v>-5.637114049449142</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7129516882003815</v>
+        <v>0.7018323682473735</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7489116486415501</v>
+        <v>-0.9235379167326454</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.507687423155848</v>
+        <v>2.402911662301191</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.5470177507905</v>
+        <v>-5.57481605067302</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8042064415076511</v>
+        <v>0.7930871215546436</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7489116486415501</v>
+        <v>-0.9235379167326454</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.574022976952669</v>
+        <v>2.469247216098012</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.345227553125342</v>
+        <v>-5.373025853007862</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5935033929631124</v>
+        <v>0.5823840730101044</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5508934564723957</v>
+        <v>-0.725519724563491</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.40141476464356</v>
+        <v>2.296639003788902</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.285336871482749</v>
+        <v>-5.313135171365269</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6877498979423251</v>
+        <v>0.6766305779893171</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4910027748298023</v>
+        <v>-0.6656290429208975</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.507639405951291</v>
+        <v>2.402863645096634</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.383077416107724</v>
+        <v>-5.410875715990243</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6632814162083789</v>
+        <v>0.6521620962553709</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5068920529627825</v>
+        <v>-0.6815183210538778</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.512733575187546</v>
+        <v>2.407957814332889</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.559415176230653</v>
+        <v>-5.587213476113172</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5912822929838786</v>
+        <v>0.5801629730308711</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.683229813085712</v>
+        <v>-0.8578560811768072</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.40546689993846</v>
+        <v>2.300691139083803</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.55872580406943</v>
+        <v>-5.586524103951949</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5900496598882965</v>
+        <v>0.578930339935289</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.683229813085712</v>
+        <v>-0.8578560811768072</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.403958517978389</v>
+        <v>2.299182757123732</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.565296769124022</v>
+        <v>-5.593095069006542</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5872841413018959</v>
+        <v>0.5761648213488879</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6898007781403049</v>
+        <v>-0.8644270462314001</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.399878806381069</v>
+        <v>2.295103045526412</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.55734279882925</v>
+        <v>-5.58514109871177</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5904657294198046</v>
+        <v>0.5793464094667966</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6898007781403049</v>
+        <v>-0.8644270462314001</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.399878806381069</v>
+        <v>2.295103045526412</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.546969422496163</v>
+        <v>-5.574767722378683</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6009968369808441</v>
+        <v>0.5898775170278361</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6794274018072176</v>
+        <v>-0.8540536698983128</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.412484589208726</v>
+        <v>2.307708828354069</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.419285112701867</v>
+        <v>-5.447083412584386</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6569629342732872</v>
+        <v>0.6458436143202797</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5517430920129212</v>
+        <v>-0.7263693601040163</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.493987548460029</v>
+        <v>2.389211787605372</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.479951703104256</v>
+        <v>-5.507750002986775</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6194509705882041</v>
+        <v>0.6083316506351961</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6334414087314548</v>
+        <v>-0.80806767682255</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.431723230904781</v>
+        <v>2.326947470050124</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.41495784317061</v>
+        <v>-5.442756143053129</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6495462171722908</v>
+        <v>0.6384268972192833</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6066107941272995</v>
+        <v>-0.7812370622183946</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.451919302277903</v>
+        <v>2.347143541423246</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.515716478927608</v>
+        <v>-5.543514778810128</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6134037025005696</v>
+        <v>0.6022843825475617</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6954363628543049</v>
+        <v>-0.8700626309454</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.402784900672778</v>
+        <v>2.298009139818121</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.471513641841708</v>
+        <v>-5.499311941724227</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.636964439862767</v>
+        <v>0.625845119909759</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6512335257684044</v>
+        <v>-0.8258597938594996</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.435186205452155</v>
+        <v>2.330410444597498</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.50849266950515</v>
+        <v>-5.53629096938767</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6205828292666373</v>
+        <v>0.6094635093136298</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6142596239770739</v>
+        <v>-0.7888858920681691</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.455780546996201</v>
+        <v>2.351004786141544</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.528550748369991</v>
+        <v>-5.55634904825251</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6638073629037406</v>
+        <v>0.6526880429507331</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6142596239770739</v>
+        <v>-0.7888858920681691</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.507028312179241</v>
+        <v>2.402252551324584</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.488620075192101</v>
+        <v>-5.51641837507462</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6782203367691499</v>
+        <v>0.6671010168161424</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5743289507991836</v>
+        <v>-0.7489552188902787</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.529427420680228</v>
+        <v>2.424651659825571</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.8645188762324</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.448149727629396</v>
+        <v>-5.475948027511915</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6893567040325022</v>
+        <v>0.6782373840794942</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5338586032364786</v>
+        <v>-0.7084848713275738</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.548657857456121</v>
+        <v>2.443882096601464</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.829275871227025</v>
+        <v>3.47039699740746</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.914549116875255</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.448149727629396</v>
+        <v>-5.305476883844451</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.6893567040325022</v>
+        <v>0.7636132456391849</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.5338586032364786</v>
+        <v>-0.5380137276601092</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.907612913861623</v>
+        <v>2.563352186894647</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240607.xlsx
+++ b/tame_output/ON/bt/strategyON_20240607.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883077</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.47039699740746</v>
+        <v>3.470396997407458</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.305476883844451</v>
+        <v>-5.305376740390993</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7636132456391849</v>
+        <v>0.7636533030205683</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.5380137276601092</v>
+        <v>-0.5379135842066516</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.563352186894647</v>
+        <v>2.563412272966722</v>
       </c>
     </row>
   </sheetData>
